--- a/data/monthly_place/【2025年10月】月次配置.xlsx
+++ b/data/monthly_place/【2025年10月】月次配置.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="600" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="92">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -186,30 +185,139 @@
   <si>
     <t>2026-10-30</t>
   </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>モバイルウェブ</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>inactive</t>
+  </si>
+  <si>
+    <t>錦糸町矯正歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（マウスピース矯正）</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -217,36 +325,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -535,14 +643,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB41"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB155"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,7 +733,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -663,7 +768,7 @@
         <v>892</v>
       </c>
       <c r="L2">
-        <v>1.634529</v>
+        <v>1.6345289999999999</v>
       </c>
       <c r="M2">
         <v>58.82758621</v>
@@ -684,13 +789,13 @@
         <v>1458</v>
       </c>
       <c r="S2">
-        <v>1170.096022</v>
+        <v>1170.0960219999999</v>
       </c>
       <c r="T2">
         <v>29</v>
       </c>
       <c r="V2">
-        <v>58.827586</v>
+        <v>58.827585999999997</v>
       </c>
       <c r="W2">
         <v>1.989026</v>
@@ -699,19 +804,19 @@
         <v>34</v>
       </c>
       <c r="Y2">
-        <v>2.331962</v>
+        <v>2.3319619999999999</v>
       </c>
       <c r="Z2">
-        <v>50.176471</v>
+        <v>50.176470999999999</v>
       </c>
       <c r="AA2">
         <v>25</v>
       </c>
       <c r="AB2">
-        <v>68.24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28">
+        <v>68.239999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -758,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="S3">
-        <v>1076.923077</v>
+        <v>1076.9230769999999</v>
       </c>
       <c r="X3">
         <v>0</v>
@@ -770,7 +875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -829,7 +934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -867,7 +972,7 @@
         <v>1.454545</v>
       </c>
       <c r="M5">
-        <v>74.22222222</v>
+        <v>74.222222220000006</v>
       </c>
       <c r="N5">
         <v>320</v>
@@ -891,19 +996,19 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>74.222222</v>
+        <v>74.222222000000002</v>
       </c>
       <c r="W5">
-        <v>1.442308</v>
+        <v>1.4423079999999999</v>
       </c>
       <c r="X5">
         <v>9</v>
       </c>
       <c r="Y5">
-        <v>1.442308</v>
+        <v>1.4423079999999999</v>
       </c>
       <c r="Z5">
-        <v>74.222222</v>
+        <v>74.222222000000002</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -912,7 +1017,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -950,7 +1055,7 @@
         <v>1.441541</v>
       </c>
       <c r="M6">
-        <v>41.425</v>
+        <v>41.424999999999997</v>
       </c>
       <c r="N6">
         <v>320</v>
@@ -968,34 +1073,34 @@
         <v>1048</v>
       </c>
       <c r="S6">
-        <v>1581.10687</v>
+        <v>1581.1068700000001</v>
       </c>
       <c r="T6">
         <v>40</v>
       </c>
       <c r="V6">
-        <v>41.425</v>
+        <v>41.424999999999997</v>
       </c>
       <c r="W6">
-        <v>3.816794</v>
+        <v>3.8167939999999998</v>
       </c>
       <c r="X6">
         <v>43</v>
       </c>
       <c r="Y6">
-        <v>4.103053</v>
+        <v>4.1030530000000001</v>
       </c>
       <c r="Z6">
-        <v>38.534884</v>
+        <v>38.534883999999998</v>
       </c>
       <c r="AA6">
         <v>33</v>
       </c>
       <c r="AB6">
-        <v>50.212121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28">
+        <v>50.212121000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1033,7 +1138,7 @@
         <v>1.584708</v>
       </c>
       <c r="M7">
-        <v>47.10344828</v>
+        <v>47.103448280000002</v>
       </c>
       <c r="N7">
         <v>160</v>
@@ -1066,19 +1171,19 @@
         <v>28</v>
       </c>
       <c r="Y7">
-        <v>2.649007</v>
+        <v>2.6490070000000001</v>
       </c>
       <c r="Z7">
-        <v>48.785714</v>
+        <v>48.785713999999999</v>
       </c>
       <c r="AA7">
         <v>22</v>
       </c>
       <c r="AB7">
-        <v>62.090909</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28">
+        <v>62.090909000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1125,7 +1230,7 @@
         <v>19</v>
       </c>
       <c r="S8">
-        <v>947.368421</v>
+        <v>947.36842100000001</v>
       </c>
       <c r="X8">
         <v>0</v>
@@ -1137,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1166,7 +1271,7 @@
         <v>29</v>
       </c>
       <c r="L9">
-        <v>1.172414</v>
+        <v>1.1724140000000001</v>
       </c>
       <c r="N9">
         <v>160</v>
@@ -1184,7 +1289,7 @@
         <v>34</v>
       </c>
       <c r="S9">
-        <v>352.941176</v>
+        <v>352.94117599999998</v>
       </c>
       <c r="X9">
         <v>0</v>
@@ -1196,7 +1301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1231,7 +1336,7 @@
         <v>486</v>
       </c>
       <c r="L10">
-        <v>1.460905</v>
+        <v>1.4609049999999999</v>
       </c>
       <c r="M10">
         <v>67</v>
@@ -1267,19 +1372,19 @@
         <v>14</v>
       </c>
       <c r="Y10">
-        <v>1.971831</v>
+        <v>1.9718309999999999</v>
       </c>
       <c r="Z10">
-        <v>62.214286</v>
+        <v>62.214286000000001</v>
       </c>
       <c r="AA10">
         <v>11</v>
       </c>
       <c r="AB10">
-        <v>79.181818</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28">
+        <v>79.181818000000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1314,7 +1419,7 @@
         <v>797</v>
       </c>
       <c r="L11">
-        <v>1.297365</v>
+        <v>1.2973650000000001</v>
       </c>
       <c r="M11">
         <v>56.3125</v>
@@ -1344,13 +1449,13 @@
         <v>56.3125</v>
       </c>
       <c r="W11">
-        <v>3.094778</v>
+        <v>3.0947779999999998</v>
       </c>
       <c r="X11">
         <v>37</v>
       </c>
       <c r="Y11">
-        <v>3.578337</v>
+        <v>3.5783369999999999</v>
       </c>
       <c r="Z11">
         <v>48.702703</v>
@@ -1359,10 +1464,10 @@
         <v>29</v>
       </c>
       <c r="AB11">
-        <v>62.137931</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28">
+        <v>62.137931000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1400,7 +1505,7 @@
         <v>1.380717</v>
       </c>
       <c r="M12">
-        <v>59.63636364</v>
+        <v>59.636363639999999</v>
       </c>
       <c r="N12">
         <v>160</v>
@@ -1427,13 +1532,13 @@
         <v>59.636364</v>
       </c>
       <c r="W12">
-        <v>1.969561</v>
+        <v>1.9695609999999999</v>
       </c>
       <c r="X12">
         <v>25</v>
       </c>
       <c r="Y12">
-        <v>2.238138</v>
+        <v>2.2381380000000002</v>
       </c>
       <c r="Z12">
         <v>52.48</v>
@@ -1442,10 +1547,10 @@
         <v>18</v>
       </c>
       <c r="AB12">
-        <v>72.888889</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28">
+        <v>72.888889000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -1480,7 +1585,7 @@
         <v>20</v>
       </c>
       <c r="L13">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="M13">
         <v>25</v>
@@ -1510,13 +1615,13 @@
         <v>25</v>
       </c>
       <c r="W13">
-        <v>4.545455</v>
+        <v>4.5454549999999996</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>4.545455</v>
+        <v>4.5454549999999996</v>
       </c>
       <c r="Z13">
         <v>25</v>
@@ -1528,7 +1633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -1587,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1622,7 +1727,7 @@
         <v>569</v>
       </c>
       <c r="L15">
-        <v>1.383128</v>
+        <v>1.3831279999999999</v>
       </c>
       <c r="M15">
         <v>93.125</v>
@@ -1643,7 +1748,7 @@
         <v>787</v>
       </c>
       <c r="S15">
-        <v>946.632783</v>
+        <v>946.63278300000002</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1661,16 +1766,16 @@
         <v>1.397713</v>
       </c>
       <c r="Z15">
-        <v>67.727273</v>
+        <v>67.727272999999997</v>
       </c>
       <c r="AA15">
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>106.428571</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28">
+        <v>106.42857100000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -1705,7 +1810,7 @@
         <v>921</v>
       </c>
       <c r="L16">
-        <v>1.352877</v>
+        <v>1.3528770000000001</v>
       </c>
       <c r="M16">
         <v>50.76923077</v>
@@ -1726,22 +1831,22 @@
         <v>1246</v>
       </c>
       <c r="S16">
-        <v>1589.085072</v>
+        <v>1589.0850720000001</v>
       </c>
       <c r="T16">
         <v>39</v>
       </c>
       <c r="V16">
-        <v>50.769231</v>
+        <v>50.769230999999998</v>
       </c>
       <c r="W16">
-        <v>3.130016</v>
+        <v>3.1300159999999999</v>
       </c>
       <c r="X16">
         <v>40</v>
       </c>
       <c r="Y16">
-        <v>3.210273</v>
+        <v>3.2102729999999999</v>
       </c>
       <c r="Z16">
         <v>49.5</v>
@@ -1753,7 +1858,7 @@
         <v>61.875</v>
       </c>
     </row>
-    <row r="17" spans="1:28">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1812,7 +1917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1847,7 +1952,7 @@
         <v>509</v>
       </c>
       <c r="L18">
-        <v>1.526523</v>
+        <v>1.5265230000000001</v>
       </c>
       <c r="M18">
         <v>97.3</v>
@@ -1877,16 +1982,16 @@
         <v>97.3</v>
       </c>
       <c r="W18">
-        <v>1.287001</v>
+        <v>1.2870010000000001</v>
       </c>
       <c r="X18">
         <v>11</v>
       </c>
       <c r="Y18">
-        <v>1.415701</v>
+        <v>1.4157010000000001</v>
       </c>
       <c r="Z18">
-        <v>88.454545</v>
+        <v>88.454544999999996</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -1895,7 +2000,7 @@
         <v>97.3</v>
       </c>
     </row>
-    <row r="19" spans="1:28">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1951,7 +2056,7 @@
         <v>29</v>
       </c>
       <c r="S19">
-        <v>965.517241</v>
+        <v>965.51724100000001</v>
       </c>
       <c r="T19">
         <v>1</v>
@@ -1960,13 +2065,13 @@
         <v>28</v>
       </c>
       <c r="W19">
-        <v>3.448276</v>
+        <v>3.4482759999999999</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
       <c r="Y19">
-        <v>3.448276</v>
+        <v>3.4482759999999999</v>
       </c>
       <c r="Z19">
         <v>28</v>
@@ -1978,7 +2083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:28">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2007,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="L20">
-        <v>1.076923</v>
+        <v>1.0769230000000001</v>
       </c>
       <c r="N20">
         <v>160</v>
@@ -2025,7 +2130,7 @@
         <v>14</v>
       </c>
       <c r="S20">
-        <v>142.857143</v>
+        <v>142.85714300000001</v>
       </c>
       <c r="X20">
         <v>0</v>
@@ -2037,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2075,7 +2180,7 @@
         <v>1.318792</v>
       </c>
       <c r="M21">
-        <v>73.83333333</v>
+        <v>73.833333330000002</v>
       </c>
       <c r="N21">
         <v>160</v>
@@ -2099,7 +2204,7 @@
         <v>6</v>
       </c>
       <c r="V21">
-        <v>73.833333</v>
+        <v>73.833332999999996</v>
       </c>
       <c r="W21">
         <v>1.526718</v>
@@ -2108,19 +2213,19 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>1.78117</v>
+        <v>1.7811699999999999</v>
       </c>
       <c r="Z21">
-        <v>63.285714</v>
+        <v>63.285713999999999</v>
       </c>
       <c r="AA21">
         <v>6</v>
       </c>
       <c r="AB21">
-        <v>73.833333</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28">
+        <v>73.833332999999996</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -2158,7 +2263,7 @@
         <v>1.624085</v>
       </c>
       <c r="M22">
-        <v>47.45454545</v>
+        <v>47.454545449999998</v>
       </c>
       <c r="N22">
         <v>160</v>
@@ -2176,34 +2281,34 @@
         <v>1996</v>
       </c>
       <c r="S22">
-        <v>1307.61523</v>
+        <v>1307.6152300000001</v>
       </c>
       <c r="T22">
         <v>55</v>
       </c>
       <c r="V22">
-        <v>47.454545</v>
+        <v>47.454545000000003</v>
       </c>
       <c r="W22">
-        <v>2.755511</v>
+        <v>2.7555109999999998</v>
       </c>
       <c r="X22">
         <v>68</v>
       </c>
       <c r="Y22">
-        <v>3.406814</v>
+        <v>3.4068139999999998</v>
       </c>
       <c r="Z22">
-        <v>38.382353</v>
+        <v>38.382353000000002</v>
       </c>
       <c r="AA22">
         <v>47</v>
       </c>
       <c r="AB22">
-        <v>55.531915</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28">
+        <v>55.531914999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>28</v>
       </c>
@@ -2238,7 +2343,7 @@
         <v>392</v>
       </c>
       <c r="L23">
-        <v>1.612245</v>
+        <v>1.6122449999999999</v>
       </c>
       <c r="M23">
         <v>103.33333333</v>
@@ -2259,7 +2364,7 @@
         <v>632</v>
       </c>
       <c r="S23">
-        <v>981.012658</v>
+        <v>981.01265799999999</v>
       </c>
       <c r="T23">
         <v>6</v>
@@ -2268,16 +2373,16 @@
         <v>103.333333</v>
       </c>
       <c r="W23">
-        <v>0.949367</v>
+        <v>0.94936699999999996</v>
       </c>
       <c r="X23">
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>1.107595</v>
+        <v>1.1075950000000001</v>
       </c>
       <c r="Z23">
-        <v>88.571429</v>
+        <v>88.571428999999995</v>
       </c>
       <c r="AA23">
         <v>6</v>
@@ -2286,7 +2391,7 @@
         <v>103.333333</v>
       </c>
     </row>
-    <row r="24" spans="1:28">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -2333,7 +2438,7 @@
         <v>29</v>
       </c>
       <c r="S24">
-        <v>517.241379</v>
+        <v>517.24137900000005</v>
       </c>
       <c r="X24">
         <v>0</v>
@@ -2345,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2392,7 +2497,7 @@
         <v>15</v>
       </c>
       <c r="S25">
-        <v>333.333333</v>
+        <v>333.33333299999998</v>
       </c>
       <c r="X25">
         <v>0</v>
@@ -2404,7 +2509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:28">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2460,7 +2565,7 @@
         <v>540</v>
       </c>
       <c r="S26">
-        <v>859.259259</v>
+        <v>859.25925900000004</v>
       </c>
       <c r="T26">
         <v>11</v>
@@ -2469,16 +2574,16 @@
         <v>42.181818</v>
       </c>
       <c r="W26">
-        <v>2.037037</v>
+        <v>2.0370370000000002</v>
       </c>
       <c r="X26">
         <v>12</v>
       </c>
       <c r="Y26">
-        <v>2.222222</v>
+        <v>2.2222219999999999</v>
       </c>
       <c r="Z26">
-        <v>38.666667</v>
+        <v>38.666666999999997</v>
       </c>
       <c r="AA26">
         <v>10</v>
@@ -2487,7 +2592,7 @@
         <v>46.4</v>
       </c>
     </row>
-    <row r="27" spans="1:28">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -2522,10 +2627,10 @@
         <v>1380</v>
       </c>
       <c r="L27">
-        <v>1.939855</v>
+        <v>1.9398550000000001</v>
       </c>
       <c r="M27">
-        <v>28.87254902</v>
+        <v>28.872549020000001</v>
       </c>
       <c r="N27">
         <v>160</v>
@@ -2543,13 +2648,13 @@
         <v>2677</v>
       </c>
       <c r="S27">
-        <v>1100.112066</v>
+        <v>1100.1120659999999</v>
       </c>
       <c r="T27">
         <v>102</v>
       </c>
       <c r="V27">
-        <v>28.872549</v>
+        <v>28.872548999999999</v>
       </c>
       <c r="W27">
         <v>3.810235</v>
@@ -2558,19 +2663,19 @@
         <v>123</v>
       </c>
       <c r="Y27">
-        <v>4.594696</v>
+        <v>4.5946959999999999</v>
       </c>
       <c r="Z27">
-        <v>23.943089</v>
+        <v>23.943089000000001</v>
       </c>
       <c r="AA27">
         <v>87</v>
       </c>
       <c r="AB27">
-        <v>33.850575</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28">
+        <v>33.850574999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2605,7 +2710,7 @@
         <v>526</v>
       </c>
       <c r="L28">
-        <v>1.321293</v>
+        <v>1.3212930000000001</v>
       </c>
       <c r="M28">
         <v>64</v>
@@ -2626,7 +2731,7 @@
         <v>695</v>
       </c>
       <c r="S28">
-        <v>1381.294964</v>
+        <v>1381.2949639999999</v>
       </c>
       <c r="T28">
         <v>15</v>
@@ -2635,13 +2740,13 @@
         <v>64</v>
       </c>
       <c r="W28">
-        <v>2.158273</v>
+        <v>2.1582729999999999</v>
       </c>
       <c r="X28">
         <v>15</v>
       </c>
       <c r="Y28">
-        <v>2.158273</v>
+        <v>2.1582729999999999</v>
       </c>
       <c r="Z28">
         <v>64</v>
@@ -2653,7 +2758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:28">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -2709,7 +2814,7 @@
         <v>19</v>
       </c>
       <c r="S29">
-        <v>1052.631579</v>
+        <v>1052.6315790000001</v>
       </c>
       <c r="T29">
         <v>1</v>
@@ -2718,13 +2823,13 @@
         <v>20</v>
       </c>
       <c r="W29">
-        <v>5.263158</v>
+        <v>5.2631579999999998</v>
       </c>
       <c r="X29">
         <v>1</v>
       </c>
       <c r="Y29">
-        <v>5.263158</v>
+        <v>5.2631579999999998</v>
       </c>
       <c r="Z29">
         <v>20</v>
@@ -2736,7 +2841,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:28">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2783,7 +2888,7 @@
         <v>27</v>
       </c>
       <c r="S30">
-        <v>481.481481</v>
+        <v>481.48148099999997</v>
       </c>
       <c r="X30">
         <v>0</v>
@@ -2795,7 +2900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>28</v>
       </c>
@@ -2830,7 +2935,7 @@
         <v>302</v>
       </c>
       <c r="L31">
-        <v>1.34106</v>
+        <v>1.3410599999999999</v>
       </c>
       <c r="M31">
         <v>56.625</v>
@@ -2866,10 +2971,10 @@
         <v>14</v>
       </c>
       <c r="Y31">
-        <v>3.45679</v>
+        <v>3.4567899999999998</v>
       </c>
       <c r="Z31">
-        <v>32.357143</v>
+        <v>32.357143000000001</v>
       </c>
       <c r="AA31">
         <v>11</v>
@@ -2878,7 +2983,7 @@
         <v>41.181818</v>
       </c>
     </row>
-    <row r="32" spans="1:28">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -2913,7 +3018,7 @@
         <v>1141</v>
       </c>
       <c r="L32">
-        <v>1.314636</v>
+        <v>1.3146359999999999</v>
       </c>
       <c r="M32">
         <v>54.6875</v>
@@ -2952,7 +3057,7 @@
         <v>3.8</v>
       </c>
       <c r="Z32">
-        <v>46.052632</v>
+        <v>46.052632000000003</v>
       </c>
       <c r="AA32">
         <v>35</v>
@@ -2961,7 +3066,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:28">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -3020,7 +3125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:28">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -3055,7 +3160,7 @@
         <v>1418</v>
       </c>
       <c r="L34">
-        <v>1.410437</v>
+        <v>1.4104369999999999</v>
       </c>
       <c r="M34">
         <v>20.85526316</v>
@@ -3082,7 +3187,7 @@
         <v>76</v>
       </c>
       <c r="V34">
-        <v>20.855263</v>
+        <v>20.855263000000001</v>
       </c>
       <c r="W34">
         <v>3.8</v>
@@ -3091,7 +3196,7 @@
         <v>88</v>
       </c>
       <c r="Y34">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="Z34">
         <v>18.011364</v>
@@ -3100,10 +3205,10 @@
         <v>72</v>
       </c>
       <c r="AB34">
-        <v>22.013889</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28">
+        <v>22.013888999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>28</v>
       </c>
@@ -3132,7 +3237,7 @@
         <v>20</v>
       </c>
       <c r="L35">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="N35">
         <v>160</v>
@@ -3162,7 +3267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>28</v>
       </c>
@@ -3218,7 +3323,7 @@
         <v>31</v>
       </c>
       <c r="S36">
-        <v>419.354839</v>
+        <v>419.35483900000003</v>
       </c>
       <c r="T36">
         <v>1</v>
@@ -3245,7 +3350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:28">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>28</v>
       </c>
@@ -3280,7 +3385,7 @@
         <v>683</v>
       </c>
       <c r="L37">
-        <v>1.256223</v>
+        <v>1.2562230000000001</v>
       </c>
       <c r="M37">
         <v>23</v>
@@ -3301,7 +3406,7 @@
         <v>858</v>
       </c>
       <c r="S37">
-        <v>777.389277</v>
+        <v>777.38927699999999</v>
       </c>
       <c r="T37">
         <v>29</v>
@@ -3316,7 +3421,7 @@
         <v>32</v>
       </c>
       <c r="Y37">
-        <v>3.729604</v>
+        <v>3.7296040000000001</v>
       </c>
       <c r="Z37">
         <v>20.84375</v>
@@ -3325,10 +3430,10 @@
         <v>26</v>
       </c>
       <c r="AB37">
-        <v>25.653846</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28">
+        <v>25.653846000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>28</v>
       </c>
@@ -3363,10 +3468,10 @@
         <v>331</v>
       </c>
       <c r="L38">
-        <v>1.229607</v>
+        <v>1.2296069999999999</v>
       </c>
       <c r="M38">
-        <v>35.78571429</v>
+        <v>35.785714290000001</v>
       </c>
       <c r="N38">
         <v>160</v>
@@ -3384,22 +3489,22 @@
         <v>407</v>
       </c>
       <c r="S38">
-        <v>1230.958231</v>
+        <v>1230.9582310000001</v>
       </c>
       <c r="T38">
         <v>14</v>
       </c>
       <c r="V38">
-        <v>35.785714</v>
+        <v>35.785713999999999</v>
       </c>
       <c r="W38">
-        <v>3.439803</v>
+        <v>3.4398029999999999</v>
       </c>
       <c r="X38">
         <v>15</v>
       </c>
       <c r="Y38">
-        <v>3.685504</v>
+        <v>3.6855039999999999</v>
       </c>
       <c r="Z38">
         <v>33.4</v>
@@ -3408,10 +3513,10 @@
         <v>13</v>
       </c>
       <c r="AB38">
-        <v>38.538462</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28">
+        <v>38.538462000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -3467,7 +3572,7 @@
         <v>30</v>
       </c>
       <c r="S39">
-        <v>933.333333</v>
+        <v>933.33333300000004</v>
       </c>
       <c r="T39">
         <v>2</v>
@@ -3476,13 +3581,13 @@
         <v>14</v>
       </c>
       <c r="W39">
-        <v>6.666667</v>
+        <v>6.6666670000000003</v>
       </c>
       <c r="X39">
         <v>2</v>
       </c>
       <c r="Y39">
-        <v>6.666667</v>
+        <v>6.6666670000000003</v>
       </c>
       <c r="Z39">
         <v>14</v>
@@ -3494,7 +3599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:28">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>28</v>
       </c>
@@ -3559,13 +3664,13 @@
         <v>12</v>
       </c>
       <c r="W40">
-        <v>6.666667</v>
+        <v>6.6666670000000003</v>
       </c>
       <c r="X40">
         <v>1</v>
       </c>
       <c r="Y40">
-        <v>6.666667</v>
+        <v>6.6666670000000003</v>
       </c>
       <c r="Z40">
         <v>12</v>
@@ -3577,7 +3682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:28">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>28</v>
       </c>
@@ -3642,13 +3747,13 @@
         <v>39</v>
       </c>
       <c r="W41">
-        <v>2.777778</v>
+        <v>2.7777780000000001</v>
       </c>
       <c r="X41">
         <v>1</v>
       </c>
       <c r="Y41">
-        <v>2.777778</v>
+        <v>2.7777780000000001</v>
       </c>
       <c r="Z41">
         <v>39</v>
@@ -3660,18 +3765,8314 @@
         <v>39</v>
       </c>
     </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F42" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42">
+        <v>7</v>
+      </c>
+      <c r="L42">
+        <v>1.285714</v>
+      </c>
+      <c r="N42" t="s">
+        <v>53</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>22</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>90</v>
+      </c>
+      <c r="R42">
+        <v>9</v>
+      </c>
+      <c r="S42">
+        <v>2444.4444440000002</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" t="s">
+        <v>41</v>
+      </c>
+      <c r="F43" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H43" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43">
+        <v>3</v>
+      </c>
+      <c r="J43" t="s">
+        <v>36</v>
+      </c>
+      <c r="K43">
+        <v>89</v>
+      </c>
+      <c r="L43">
+        <v>1.9213480000000001</v>
+      </c>
+      <c r="M43">
+        <v>36.333333330000002</v>
+      </c>
+      <c r="N43" t="s">
+        <v>53</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>109</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>90</v>
+      </c>
+      <c r="R43">
+        <v>171</v>
+      </c>
+      <c r="S43">
+        <v>637.42690100000004</v>
+      </c>
+      <c r="T43">
+        <v>3</v>
+      </c>
+      <c r="V43">
+        <v>36.333333000000003</v>
+      </c>
+      <c r="W43">
+        <v>1.754386</v>
+      </c>
+      <c r="X43">
+        <v>3</v>
+      </c>
+      <c r="Y43">
+        <v>1.754386</v>
+      </c>
+      <c r="Z43">
+        <v>36.333333000000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" t="s">
+        <v>35</v>
+      </c>
+      <c r="I44">
+        <v>56</v>
+      </c>
+      <c r="J44" t="s">
+        <v>36</v>
+      </c>
+      <c r="K44">
+        <v>1813</v>
+      </c>
+      <c r="L44">
+        <v>3.5410919999999999</v>
+      </c>
+      <c r="M44">
+        <v>99.375</v>
+      </c>
+      <c r="N44" t="s">
+        <v>53</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>5565</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>90</v>
+      </c>
+      <c r="R44">
+        <v>6420</v>
+      </c>
+      <c r="S44">
+        <v>866.82243000000005</v>
+      </c>
+      <c r="T44">
+        <v>56</v>
+      </c>
+      <c r="V44">
+        <v>99.375</v>
+      </c>
+      <c r="W44">
+        <v>0.87227399999999999</v>
+      </c>
+      <c r="X44">
+        <v>60</v>
+      </c>
+      <c r="Y44">
+        <v>0.93457900000000005</v>
+      </c>
+      <c r="Z44">
+        <v>92.75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" t="s">
+        <v>32</v>
+      </c>
+      <c r="F45" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45" t="s">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>374</v>
+      </c>
+      <c r="L45">
+        <v>1.1550800000000001</v>
+      </c>
+      <c r="M45">
+        <v>134</v>
+      </c>
+      <c r="N45" t="s">
+        <v>53</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>536</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>88</v>
+      </c>
+      <c r="R45">
+        <v>432</v>
+      </c>
+      <c r="S45">
+        <v>1240.7407410000001</v>
+      </c>
+      <c r="T45">
+        <v>4</v>
+      </c>
+      <c r="V45">
+        <v>134</v>
+      </c>
+      <c r="W45">
+        <v>0.92592600000000003</v>
+      </c>
+      <c r="X45">
+        <v>4</v>
+      </c>
+      <c r="Y45">
+        <v>0.92592600000000003</v>
+      </c>
+      <c r="Z45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46">
+        <v>11</v>
+      </c>
+      <c r="L46">
+        <v>1.181818</v>
+      </c>
+      <c r="N46" t="s">
+        <v>53</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>10</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>88</v>
+      </c>
+      <c r="R46">
+        <v>13</v>
+      </c>
+      <c r="S46">
+        <v>769.23076900000001</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" t="s">
+        <v>33</v>
+      </c>
+      <c r="G47" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" t="s">
+        <v>35</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="N47" t="s">
+        <v>53</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>88</v>
+      </c>
+      <c r="R47">
+        <v>2</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>28</v>
+      </c>
+      <c r="B48" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" t="s">
+        <v>33</v>
+      </c>
+      <c r="G48" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" t="s">
+        <v>35</v>
+      </c>
+      <c r="K48">
+        <v>210</v>
+      </c>
+      <c r="L48">
+        <v>1.1857139999999999</v>
+      </c>
+      <c r="N48" t="s">
+        <v>53</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>173</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>88</v>
+      </c>
+      <c r="R48">
+        <v>249</v>
+      </c>
+      <c r="S48">
+        <v>694.77911600000004</v>
+      </c>
+      <c r="X48">
+        <v>1</v>
+      </c>
+      <c r="Y48">
+        <v>0.40160600000000002</v>
+      </c>
+      <c r="Z48">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" t="s">
+        <v>35</v>
+      </c>
+      <c r="I49">
+        <v>72</v>
+      </c>
+      <c r="J49" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49">
+        <v>4075</v>
+      </c>
+      <c r="L49">
+        <v>1.2841720000000001</v>
+      </c>
+      <c r="M49">
+        <v>75.027777779999994</v>
+      </c>
+      <c r="N49" t="s">
+        <v>53</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>5402</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>88</v>
+      </c>
+      <c r="R49">
+        <v>5233</v>
+      </c>
+      <c r="S49">
+        <v>1032.2950510000001</v>
+      </c>
+      <c r="T49">
+        <v>72</v>
+      </c>
+      <c r="V49">
+        <v>75.027777999999998</v>
+      </c>
+      <c r="W49">
+        <v>1.3758840000000001</v>
+      </c>
+      <c r="X49">
+        <v>75</v>
+      </c>
+      <c r="Y49">
+        <v>1.4332119999999999</v>
+      </c>
+      <c r="Z49">
+        <v>72.026667000000003</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B50" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>32</v>
+      </c>
+      <c r="F50" t="s">
+        <v>33</v>
+      </c>
+      <c r="G50" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I50">
+        <v>29</v>
+      </c>
+      <c r="J50" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50">
+        <v>1221</v>
+      </c>
+      <c r="L50">
+        <v>1.2506139999999999</v>
+      </c>
+      <c r="M50">
+        <v>56.517241380000002</v>
+      </c>
+      <c r="N50" t="s">
+        <v>53</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>1639</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>85</v>
+      </c>
+      <c r="R50">
+        <v>1527</v>
+      </c>
+      <c r="S50">
+        <v>1073.3464309999999</v>
+      </c>
+      <c r="T50">
+        <v>29</v>
+      </c>
+      <c r="V50">
+        <v>56.517240999999999</v>
+      </c>
+      <c r="W50">
+        <v>1.899149</v>
+      </c>
+      <c r="X50">
+        <v>32</v>
+      </c>
+      <c r="Y50">
+        <v>2.095612</v>
+      </c>
+      <c r="Z50">
+        <v>51.21875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51" t="s">
+        <v>68</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51">
+        <v>1</v>
+      </c>
+      <c r="N51" t="s">
+        <v>53</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>85</v>
+      </c>
+      <c r="R51">
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <v>1000</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" t="s">
+        <v>29</v>
+      </c>
+      <c r="C52" t="s">
+        <v>87</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>33</v>
+      </c>
+      <c r="G52" t="s">
+        <v>68</v>
+      </c>
+      <c r="H52" t="s">
+        <v>35</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>36</v>
+      </c>
+      <c r="K52">
+        <v>36</v>
+      </c>
+      <c r="L52">
+        <v>1.1944440000000001</v>
+      </c>
+      <c r="M52">
+        <v>21</v>
+      </c>
+      <c r="N52" t="s">
+        <v>53</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>21</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>85</v>
+      </c>
+      <c r="R52">
+        <v>43</v>
+      </c>
+      <c r="S52">
+        <v>488.37209300000001</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="V52">
+        <v>21</v>
+      </c>
+      <c r="W52">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="Y52">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="Z52">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" t="s">
+        <v>29</v>
+      </c>
+      <c r="C53" t="s">
+        <v>87</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>40</v>
+      </c>
+      <c r="F53" t="s">
+        <v>33</v>
+      </c>
+      <c r="G53" t="s">
+        <v>68</v>
+      </c>
+      <c r="H53" t="s">
+        <v>35</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>36</v>
+      </c>
+      <c r="K53">
+        <v>14</v>
+      </c>
+      <c r="L53">
+        <v>1.071429</v>
+      </c>
+      <c r="M53">
+        <v>1</v>
+      </c>
+      <c r="N53" t="s">
+        <v>53</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>85</v>
+      </c>
+      <c r="R53">
+        <v>15</v>
+      </c>
+      <c r="S53">
+        <v>66.666667000000004</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="V53">
+        <v>1</v>
+      </c>
+      <c r="W53">
+        <v>6.6666670000000003</v>
+      </c>
+      <c r="X53">
+        <v>1</v>
+      </c>
+      <c r="Y53">
+        <v>6.6666670000000003</v>
+      </c>
+      <c r="Z53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" t="s">
+        <v>29</v>
+      </c>
+      <c r="C54" t="s">
+        <v>87</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" t="s">
+        <v>33</v>
+      </c>
+      <c r="G54" t="s">
+        <v>68</v>
+      </c>
+      <c r="H54" t="s">
+        <v>35</v>
+      </c>
+      <c r="I54">
+        <v>10</v>
+      </c>
+      <c r="J54" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54">
+        <v>375</v>
+      </c>
+      <c r="L54">
+        <v>1.1333329999999999</v>
+      </c>
+      <c r="M54">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="N54" t="s">
+        <v>53</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>368</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>85</v>
+      </c>
+      <c r="R54">
+        <v>425</v>
+      </c>
+      <c r="S54">
+        <v>865.88235299999997</v>
+      </c>
+      <c r="T54">
+        <v>10</v>
+      </c>
+      <c r="V54">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="W54">
+        <v>2.3529409999999999</v>
+      </c>
+      <c r="X54">
+        <v>12</v>
+      </c>
+      <c r="Y54">
+        <v>2.8235290000000002</v>
+      </c>
+      <c r="Z54">
+        <v>30.666667</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+      <c r="G55" t="s">
+        <v>68</v>
+      </c>
+      <c r="H55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I55">
+        <v>49</v>
+      </c>
+      <c r="J55" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55">
+        <v>2678</v>
+      </c>
+      <c r="L55">
+        <v>1.2837940000000001</v>
+      </c>
+      <c r="M55">
+        <v>86.857142859999996</v>
+      </c>
+      <c r="N55" t="s">
+        <v>53</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>4256</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>85</v>
+      </c>
+      <c r="R55">
+        <v>3438</v>
+      </c>
+      <c r="S55">
+        <v>1237.9290289999999</v>
+      </c>
+      <c r="T55">
+        <v>49</v>
+      </c>
+      <c r="V55">
+        <v>86.857142999999994</v>
+      </c>
+      <c r="W55">
+        <v>1.4252469999999999</v>
+      </c>
+      <c r="X55">
+        <v>55</v>
+      </c>
+      <c r="Y55">
+        <v>1.5997669999999999</v>
+      </c>
+      <c r="Z55">
+        <v>77.381817999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" t="s">
+        <v>29</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56" t="s">
+        <v>68</v>
+      </c>
+      <c r="H56" t="s">
+        <v>35</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="N56" t="s">
+        <v>53</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>85</v>
+      </c>
+      <c r="R56">
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>28</v>
+      </c>
+      <c r="B57" t="s">
+        <v>29</v>
+      </c>
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G57" t="s">
+        <v>68</v>
+      </c>
+      <c r="H57" t="s">
+        <v>35</v>
+      </c>
+      <c r="I57">
+        <v>12</v>
+      </c>
+      <c r="J57" t="s">
+        <v>36</v>
+      </c>
+      <c r="K57">
+        <v>245</v>
+      </c>
+      <c r="L57">
+        <v>1.253061</v>
+      </c>
+      <c r="M57">
+        <v>17</v>
+      </c>
+      <c r="N57" t="s">
+        <v>53</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>204</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>85</v>
+      </c>
+      <c r="R57">
+        <v>307</v>
+      </c>
+      <c r="S57">
+        <v>664.49511399999994</v>
+      </c>
+      <c r="T57">
+        <v>12</v>
+      </c>
+      <c r="V57">
+        <v>17</v>
+      </c>
+      <c r="W57">
+        <v>3.908795</v>
+      </c>
+      <c r="X57">
+        <v>16</v>
+      </c>
+      <c r="Y57">
+        <v>5.2117259999999996</v>
+      </c>
+      <c r="Z57">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" t="s">
+        <v>86</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" t="s">
+        <v>56</v>
+      </c>
+      <c r="G58" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" t="s">
+        <v>35</v>
+      </c>
+      <c r="K58">
+        <v>2</v>
+      </c>
+      <c r="L58">
+        <v>1</v>
+      </c>
+      <c r="N58" t="s">
+        <v>53</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>85</v>
+      </c>
+      <c r="R58">
+        <v>2</v>
+      </c>
+      <c r="S58">
+        <v>500</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>28</v>
+      </c>
+      <c r="B59" t="s">
+        <v>29</v>
+      </c>
+      <c r="C59" t="s">
+        <v>86</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" t="s">
+        <v>33</v>
+      </c>
+      <c r="G59" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" t="s">
+        <v>35</v>
+      </c>
+      <c r="I59">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>36</v>
+      </c>
+      <c r="K59">
+        <v>20</v>
+      </c>
+      <c r="L59">
+        <v>1.05</v>
+      </c>
+      <c r="M59">
+        <v>13</v>
+      </c>
+      <c r="N59" t="s">
+        <v>53</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>13</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>85</v>
+      </c>
+      <c r="R59">
+        <v>21</v>
+      </c>
+      <c r="S59">
+        <v>619.04761900000005</v>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+      <c r="V59">
+        <v>13</v>
+      </c>
+      <c r="W59">
+        <v>4.7619049999999996</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="Y59">
+        <v>4.7619049999999996</v>
+      </c>
+      <c r="Z59">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B60" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" t="s">
+        <v>86</v>
+      </c>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" t="s">
+        <v>68</v>
+      </c>
+      <c r="H60" t="s">
+        <v>35</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60" t="s">
+        <v>36</v>
+      </c>
+      <c r="K60">
+        <v>69</v>
+      </c>
+      <c r="L60">
+        <v>1.289855</v>
+      </c>
+      <c r="M60">
+        <v>8.5</v>
+      </c>
+      <c r="N60" t="s">
+        <v>53</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>17</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>85</v>
+      </c>
+      <c r="R60">
+        <v>89</v>
+      </c>
+      <c r="S60">
+        <v>191.011236</v>
+      </c>
+      <c r="T60">
+        <v>2</v>
+      </c>
+      <c r="V60">
+        <v>8.5</v>
+      </c>
+      <c r="W60">
+        <v>2.2471909999999999</v>
+      </c>
+      <c r="X60">
+        <v>3</v>
+      </c>
+      <c r="Y60">
+        <v>3.370787</v>
+      </c>
+      <c r="Z60">
+        <v>5.6666670000000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>28</v>
+      </c>
+      <c r="B61" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" t="s">
+        <v>86</v>
+      </c>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" t="s">
+        <v>33</v>
+      </c>
+      <c r="G61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H61" t="s">
+        <v>35</v>
+      </c>
+      <c r="I61">
+        <v>3</v>
+      </c>
+      <c r="J61" t="s">
+        <v>36</v>
+      </c>
+      <c r="K61">
+        <v>144</v>
+      </c>
+      <c r="L61">
+        <v>1.1875</v>
+      </c>
+      <c r="M61">
+        <v>36.333333330000002</v>
+      </c>
+      <c r="N61" t="s">
+        <v>53</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>109</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>85</v>
+      </c>
+      <c r="R61">
+        <v>171</v>
+      </c>
+      <c r="S61">
+        <v>637.42690100000004</v>
+      </c>
+      <c r="T61">
+        <v>3</v>
+      </c>
+      <c r="V61">
+        <v>36.333333000000003</v>
+      </c>
+      <c r="W61">
+        <v>1.754386</v>
+      </c>
+      <c r="X61">
+        <v>3</v>
+      </c>
+      <c r="Y61">
+        <v>1.754386</v>
+      </c>
+      <c r="Z61">
+        <v>36.333333000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>28</v>
+      </c>
+      <c r="B62" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+      <c r="G62" t="s">
+        <v>68</v>
+      </c>
+      <c r="H62" t="s">
+        <v>35</v>
+      </c>
+      <c r="I62">
+        <v>323</v>
+      </c>
+      <c r="J62" t="s">
+        <v>36</v>
+      </c>
+      <c r="K62">
+        <v>3708</v>
+      </c>
+      <c r="L62">
+        <v>1.276969</v>
+      </c>
+      <c r="M62">
+        <v>17.547987620000001</v>
+      </c>
+      <c r="N62" t="s">
+        <v>53</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>5668</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>85</v>
+      </c>
+      <c r="R62">
+        <v>4735</v>
+      </c>
+      <c r="S62">
+        <v>1197.0432949999999</v>
+      </c>
+      <c r="T62">
+        <v>323</v>
+      </c>
+      <c r="V62">
+        <v>17.547988</v>
+      </c>
+      <c r="W62">
+        <v>6.821542</v>
+      </c>
+      <c r="X62">
+        <v>331</v>
+      </c>
+      <c r="Y62">
+        <v>6.9904960000000003</v>
+      </c>
+      <c r="Z62">
+        <v>17.123867000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" t="s">
+        <v>29</v>
+      </c>
+      <c r="C63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" t="s">
+        <v>32</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+      <c r="G63" t="s">
+        <v>63</v>
+      </c>
+      <c r="H63" t="s">
+        <v>35</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63" t="s">
+        <v>36</v>
+      </c>
+      <c r="K63">
+        <v>892</v>
+      </c>
+      <c r="L63">
+        <v>1.5022420000000001</v>
+      </c>
+      <c r="M63">
+        <v>42.47619048</v>
+      </c>
+      <c r="N63" t="s">
+        <v>53</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>1784</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>83</v>
+      </c>
+      <c r="R63">
+        <v>1340</v>
+      </c>
+      <c r="S63">
+        <v>1331.343284</v>
+      </c>
+      <c r="T63">
+        <v>42</v>
+      </c>
+      <c r="V63">
+        <v>42.476190000000003</v>
+      </c>
+      <c r="W63">
+        <v>3.134328</v>
+      </c>
+      <c r="X63">
+        <v>42</v>
+      </c>
+      <c r="Y63">
+        <v>3.134328</v>
+      </c>
+      <c r="Z63">
+        <v>42.476190000000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64" t="s">
+        <v>56</v>
+      </c>
+      <c r="G64" t="s">
+        <v>63</v>
+      </c>
+      <c r="H64" t="s">
+        <v>35</v>
+      </c>
+      <c r="K64">
+        <v>2</v>
+      </c>
+      <c r="L64">
+        <v>1</v>
+      </c>
+      <c r="N64" t="s">
+        <v>53</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>83</v>
+      </c>
+      <c r="R64">
+        <v>2</v>
+      </c>
+      <c r="S64">
+        <v>1000</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C65" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65" t="s">
+        <v>31</v>
+      </c>
+      <c r="E65" t="s">
+        <v>39</v>
+      </c>
+      <c r="F65" t="s">
+        <v>33</v>
+      </c>
+      <c r="G65" t="s">
+        <v>63</v>
+      </c>
+      <c r="H65" t="s">
+        <v>35</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="J65" t="s">
+        <v>36</v>
+      </c>
+      <c r="K65">
+        <v>67</v>
+      </c>
+      <c r="L65">
+        <v>1.567164</v>
+      </c>
+      <c r="M65">
+        <v>47</v>
+      </c>
+      <c r="N65" t="s">
+        <v>53</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>94</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>83</v>
+      </c>
+      <c r="R65">
+        <v>105</v>
+      </c>
+      <c r="S65">
+        <v>895.23809500000004</v>
+      </c>
+      <c r="T65">
+        <v>2</v>
+      </c>
+      <c r="V65">
+        <v>47</v>
+      </c>
+      <c r="W65">
+        <v>1.9047620000000001</v>
+      </c>
+      <c r="X65">
+        <v>2</v>
+      </c>
+      <c r="Y65">
+        <v>1.9047620000000001</v>
+      </c>
+      <c r="Z65">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" t="s">
+        <v>29</v>
+      </c>
+      <c r="C66" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" t="s">
+        <v>40</v>
+      </c>
+      <c r="F66" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" t="s">
+        <v>63</v>
+      </c>
+      <c r="H66" t="s">
+        <v>35</v>
+      </c>
+      <c r="K66">
+        <v>141</v>
+      </c>
+      <c r="L66">
+        <v>1.382979</v>
+      </c>
+      <c r="N66" t="s">
+        <v>53</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>73</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>83</v>
+      </c>
+      <c r="R66">
+        <v>195</v>
+      </c>
+      <c r="S66">
+        <v>374.35897399999999</v>
+      </c>
+      <c r="X66">
+        <v>0</v>
+      </c>
+      <c r="Y66">
+        <v>0</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" t="s">
+        <v>33</v>
+      </c>
+      <c r="G67" t="s">
+        <v>63</v>
+      </c>
+      <c r="H67" t="s">
+        <v>35</v>
+      </c>
+      <c r="I67">
+        <v>37</v>
+      </c>
+      <c r="J67" t="s">
+        <v>36</v>
+      </c>
+      <c r="K67">
+        <v>893</v>
+      </c>
+      <c r="L67">
+        <v>1.344905</v>
+      </c>
+      <c r="M67">
+        <v>32.891891889999997</v>
+      </c>
+      <c r="N67" t="s">
+        <v>53</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>1217</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>83</v>
+      </c>
+      <c r="R67">
+        <v>1201</v>
+      </c>
+      <c r="S67">
+        <v>1013.322231</v>
+      </c>
+      <c r="T67">
+        <v>37</v>
+      </c>
+      <c r="V67">
+        <v>32.891891999999999</v>
+      </c>
+      <c r="W67">
+        <v>3.0807660000000001</v>
+      </c>
+      <c r="X67">
+        <v>37</v>
+      </c>
+      <c r="Y67">
+        <v>3.0807660000000001</v>
+      </c>
+      <c r="Z67">
+        <v>32.891891999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>28</v>
+      </c>
+      <c r="B68" t="s">
+        <v>29</v>
+      </c>
+      <c r="C68" t="s">
+        <v>84</v>
+      </c>
+      <c r="D68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" t="s">
+        <v>33</v>
+      </c>
+      <c r="G68" t="s">
+        <v>63</v>
+      </c>
+      <c r="H68" t="s">
+        <v>35</v>
+      </c>
+      <c r="I68">
+        <v>50</v>
+      </c>
+      <c r="J68" t="s">
+        <v>36</v>
+      </c>
+      <c r="K68">
+        <v>2079</v>
+      </c>
+      <c r="L68">
+        <v>1.221741</v>
+      </c>
+      <c r="M68">
+        <v>64.12</v>
+      </c>
+      <c r="N68" t="s">
+        <v>53</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>3206</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>83</v>
+      </c>
+      <c r="R68">
+        <v>2540</v>
+      </c>
+      <c r="S68">
+        <v>1262.2047239999999</v>
+      </c>
+      <c r="T68">
+        <v>50</v>
+      </c>
+      <c r="V68">
+        <v>64.12</v>
+      </c>
+      <c r="W68">
+        <v>1.968504</v>
+      </c>
+      <c r="X68">
+        <v>53</v>
+      </c>
+      <c r="Y68">
+        <v>2.086614</v>
+      </c>
+      <c r="Z68">
+        <v>60.490566000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F69" t="s">
+        <v>33</v>
+      </c>
+      <c r="G69" t="s">
+        <v>68</v>
+      </c>
+      <c r="H69" t="s">
+        <v>35</v>
+      </c>
+      <c r="I69">
+        <v>24</v>
+      </c>
+      <c r="J69" t="s">
+        <v>36</v>
+      </c>
+      <c r="K69">
+        <v>979</v>
+      </c>
+      <c r="L69">
+        <v>1.465781</v>
+      </c>
+      <c r="M69">
+        <v>43.708333330000002</v>
+      </c>
+      <c r="N69" t="s">
+        <v>53</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>1049</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>79</v>
+      </c>
+      <c r="R69">
+        <v>1435</v>
+      </c>
+      <c r="S69">
+        <v>731.01045299999998</v>
+      </c>
+      <c r="T69">
+        <v>24</v>
+      </c>
+      <c r="V69">
+        <v>43.708333000000003</v>
+      </c>
+      <c r="W69">
+        <v>1.672474</v>
+      </c>
+      <c r="X69">
+        <v>26</v>
+      </c>
+      <c r="Y69">
+        <v>1.811847</v>
+      </c>
+      <c r="Z69">
+        <v>40.346153999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" t="s">
+        <v>29</v>
+      </c>
+      <c r="C70" t="s">
+        <v>82</v>
+      </c>
+      <c r="D70" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" t="s">
+        <v>39</v>
+      </c>
+      <c r="F70" t="s">
+        <v>33</v>
+      </c>
+      <c r="G70" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" t="s">
+        <v>35</v>
+      </c>
+      <c r="I70">
+        <v>3</v>
+      </c>
+      <c r="J70" t="s">
+        <v>36</v>
+      </c>
+      <c r="K70">
+        <v>49</v>
+      </c>
+      <c r="L70">
+        <v>1.3877550000000001</v>
+      </c>
+      <c r="M70">
+        <v>13</v>
+      </c>
+      <c r="N70" t="s">
+        <v>53</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>39</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>79</v>
+      </c>
+      <c r="R70">
+        <v>68</v>
+      </c>
+      <c r="S70">
+        <v>573.52941199999998</v>
+      </c>
+      <c r="T70">
+        <v>3</v>
+      </c>
+      <c r="V70">
+        <v>13</v>
+      </c>
+      <c r="W70">
+        <v>4.4117649999999999</v>
+      </c>
+      <c r="X70">
+        <v>4</v>
+      </c>
+      <c r="Y70">
+        <v>5.8823530000000002</v>
+      </c>
+      <c r="Z70">
+        <v>9.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" t="s">
+        <v>29</v>
+      </c>
+      <c r="C71" t="s">
+        <v>82</v>
+      </c>
+      <c r="D71" t="s">
+        <v>31</v>
+      </c>
+      <c r="E71" t="s">
+        <v>40</v>
+      </c>
+      <c r="F71" t="s">
+        <v>33</v>
+      </c>
+      <c r="G71" t="s">
+        <v>68</v>
+      </c>
+      <c r="H71" t="s">
+        <v>35</v>
+      </c>
+      <c r="K71">
+        <v>38</v>
+      </c>
+      <c r="L71">
+        <v>1.236842</v>
+      </c>
+      <c r="N71" t="s">
+        <v>53</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>11</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>79</v>
+      </c>
+      <c r="R71">
+        <v>47</v>
+      </c>
+      <c r="S71">
+        <v>234.042553</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>29</v>
+      </c>
+      <c r="C72" t="s">
+        <v>82</v>
+      </c>
+      <c r="D72" t="s">
+        <v>31</v>
+      </c>
+      <c r="E72" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" t="s">
+        <v>33</v>
+      </c>
+      <c r="G72" t="s">
+        <v>68</v>
+      </c>
+      <c r="H72" t="s">
+        <v>35</v>
+      </c>
+      <c r="I72">
+        <v>11</v>
+      </c>
+      <c r="J72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K72">
+        <v>583</v>
+      </c>
+      <c r="L72">
+        <v>1.3876500000000001</v>
+      </c>
+      <c r="M72">
+        <v>55.909090910000003</v>
+      </c>
+      <c r="N72" t="s">
+        <v>53</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>615</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>79</v>
+      </c>
+      <c r="R72">
+        <v>809</v>
+      </c>
+      <c r="S72">
+        <v>760.19777499999998</v>
+      </c>
+      <c r="T72">
+        <v>11</v>
+      </c>
+      <c r="V72">
+        <v>55.909090999999997</v>
+      </c>
+      <c r="W72">
+        <v>1.3597030000000001</v>
+      </c>
+      <c r="X72">
+        <v>15</v>
+      </c>
+      <c r="Y72">
+        <v>1.854141</v>
+      </c>
+      <c r="Z72">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" t="s">
+        <v>29</v>
+      </c>
+      <c r="C73" t="s">
+        <v>82</v>
+      </c>
+      <c r="D73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" t="s">
+        <v>33</v>
+      </c>
+      <c r="G73" t="s">
+        <v>68</v>
+      </c>
+      <c r="H73" t="s">
+        <v>35</v>
+      </c>
+      <c r="I73">
+        <v>101</v>
+      </c>
+      <c r="J73" t="s">
+        <v>36</v>
+      </c>
+      <c r="K73">
+        <v>2689</v>
+      </c>
+      <c r="L73">
+        <v>1.3748610000000001</v>
+      </c>
+      <c r="M73">
+        <v>44.465346529999998</v>
+      </c>
+      <c r="N73" t="s">
+        <v>53</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>4491</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>79</v>
+      </c>
+      <c r="R73">
+        <v>3697</v>
+      </c>
+      <c r="S73">
+        <v>1214.7687309999999</v>
+      </c>
+      <c r="T73">
+        <v>101</v>
+      </c>
+      <c r="V73">
+        <v>44.465347000000001</v>
+      </c>
+      <c r="W73">
+        <v>2.7319450000000001</v>
+      </c>
+      <c r="X73">
+        <v>108</v>
+      </c>
+      <c r="Y73">
+        <v>2.9212880000000001</v>
+      </c>
+      <c r="Z73">
+        <v>41.583333000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" t="s">
+        <v>31</v>
+      </c>
+      <c r="E74" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" t="s">
+        <v>56</v>
+      </c>
+      <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" t="s">
+        <v>35</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="N74" t="s">
+        <v>53</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>79</v>
+      </c>
+      <c r="R74">
+        <v>2</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" t="s">
+        <v>29</v>
+      </c>
+      <c r="C75" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75" t="s">
+        <v>32</v>
+      </c>
+      <c r="F75" t="s">
+        <v>33</v>
+      </c>
+      <c r="G75" t="s">
+        <v>68</v>
+      </c>
+      <c r="H75" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75">
+        <v>32</v>
+      </c>
+      <c r="J75" t="s">
+        <v>36</v>
+      </c>
+      <c r="K75">
+        <v>1297</v>
+      </c>
+      <c r="L75">
+        <v>1.4325369999999999</v>
+      </c>
+      <c r="M75">
+        <v>42.78125</v>
+      </c>
+      <c r="N75" t="s">
+        <v>53</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>1369</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>79</v>
+      </c>
+      <c r="R75">
+        <v>1858</v>
+      </c>
+      <c r="S75">
+        <v>736.81377799999996</v>
+      </c>
+      <c r="T75">
+        <v>32</v>
+      </c>
+      <c r="V75">
+        <v>42.78125</v>
+      </c>
+      <c r="W75">
+        <v>1.7222820000000001</v>
+      </c>
+      <c r="X75">
+        <v>35</v>
+      </c>
+      <c r="Y75">
+        <v>1.8837459999999999</v>
+      </c>
+      <c r="Z75">
+        <v>39.114286</v>
+      </c>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" t="s">
+        <v>81</v>
+      </c>
+      <c r="D76" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" t="s">
+        <v>32</v>
+      </c>
+      <c r="F76" t="s">
+        <v>56</v>
+      </c>
+      <c r="G76" t="s">
+        <v>68</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+      <c r="L76">
+        <v>1</v>
+      </c>
+      <c r="N76" t="s">
+        <v>53</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>2</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>79</v>
+      </c>
+      <c r="R76">
+        <v>2</v>
+      </c>
+      <c r="S76">
+        <v>1000</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>28</v>
+      </c>
+      <c r="B77" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" t="s">
+        <v>81</v>
+      </c>
+      <c r="D77" t="s">
+        <v>31</v>
+      </c>
+      <c r="E77" t="s">
+        <v>39</v>
+      </c>
+      <c r="F77" t="s">
+        <v>33</v>
+      </c>
+      <c r="G77" t="s">
+        <v>68</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>36</v>
+      </c>
+      <c r="K77">
+        <v>60</v>
+      </c>
+      <c r="L77">
+        <v>1.316667</v>
+      </c>
+      <c r="M77">
+        <v>46</v>
+      </c>
+      <c r="N77" t="s">
+        <v>53</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>46</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>79</v>
+      </c>
+      <c r="R77">
+        <v>79</v>
+      </c>
+      <c r="S77">
+        <v>582.27848100000006</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="V77">
+        <v>46</v>
+      </c>
+      <c r="W77">
+        <v>1.2658229999999999</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>1.2658229999999999</v>
+      </c>
+      <c r="Z77">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>28</v>
+      </c>
+      <c r="B78" t="s">
+        <v>29</v>
+      </c>
+      <c r="C78" t="s">
+        <v>81</v>
+      </c>
+      <c r="D78" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" t="s">
+        <v>40</v>
+      </c>
+      <c r="F78" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" t="s">
+        <v>68</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="K78">
+        <v>49</v>
+      </c>
+      <c r="L78">
+        <v>1.4081630000000001</v>
+      </c>
+      <c r="N78" t="s">
+        <v>53</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>14</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>79</v>
+      </c>
+      <c r="R78">
+        <v>69</v>
+      </c>
+      <c r="S78">
+        <v>202.898551</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C79" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" t="s">
+        <v>31</v>
+      </c>
+      <c r="E79" t="s">
+        <v>41</v>
+      </c>
+      <c r="F79" t="s">
+        <v>33</v>
+      </c>
+      <c r="G79" t="s">
+        <v>68</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79">
+        <v>45</v>
+      </c>
+      <c r="J79" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79">
+        <v>1147</v>
+      </c>
+      <c r="L79">
+        <v>1.5013080000000001</v>
+      </c>
+      <c r="M79">
+        <v>29.311111109999999</v>
+      </c>
+      <c r="N79" t="s">
+        <v>53</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>1319</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>79</v>
+      </c>
+      <c r="R79">
+        <v>1722</v>
+      </c>
+      <c r="S79">
+        <v>765.96980299999996</v>
+      </c>
+      <c r="T79">
+        <v>45</v>
+      </c>
+      <c r="V79">
+        <v>29.311111</v>
+      </c>
+      <c r="W79">
+        <v>2.6132399999999998</v>
+      </c>
+      <c r="X79">
+        <v>53</v>
+      </c>
+      <c r="Y79">
+        <v>3.0778159999999999</v>
+      </c>
+      <c r="Z79">
+        <v>24.886792</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>28</v>
+      </c>
+      <c r="B80" t="s">
+        <v>29</v>
+      </c>
+      <c r="C80" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" t="s">
+        <v>31</v>
+      </c>
+      <c r="E80" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" t="s">
+        <v>33</v>
+      </c>
+      <c r="G80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80">
+        <v>92</v>
+      </c>
+      <c r="J80" t="s">
+        <v>36</v>
+      </c>
+      <c r="K80">
+        <v>1867</v>
+      </c>
+      <c r="L80">
+        <v>1.5190140000000001</v>
+      </c>
+      <c r="M80">
+        <v>35.858695650000001</v>
+      </c>
+      <c r="N80" t="s">
+        <v>53</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>3299</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>79</v>
+      </c>
+      <c r="R80">
+        <v>2836</v>
+      </c>
+      <c r="S80">
+        <v>1163.25811</v>
+      </c>
+      <c r="T80">
+        <v>92</v>
+      </c>
+      <c r="V80">
+        <v>35.858696000000002</v>
+      </c>
+      <c r="W80">
+        <v>3.2440060000000002</v>
+      </c>
+      <c r="X80">
+        <v>101</v>
+      </c>
+      <c r="Y80">
+        <v>3.5613540000000001</v>
+      </c>
+      <c r="Z80">
+        <v>32.663366000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81" t="s">
+        <v>31</v>
+      </c>
+      <c r="E81" t="s">
+        <v>32</v>
+      </c>
+      <c r="F81" t="s">
+        <v>33</v>
+      </c>
+      <c r="G81" t="s">
+        <v>68</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81">
+        <v>6</v>
+      </c>
+      <c r="J81" t="s">
+        <v>36</v>
+      </c>
+      <c r="K81">
+        <v>330</v>
+      </c>
+      <c r="L81">
+        <v>1.2090909999999999</v>
+      </c>
+      <c r="M81">
+        <v>54</v>
+      </c>
+      <c r="N81" t="s">
+        <v>53</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>324</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>79</v>
+      </c>
+      <c r="R81">
+        <v>399</v>
+      </c>
+      <c r="S81">
+        <v>812.03007500000001</v>
+      </c>
+      <c r="T81">
+        <v>6</v>
+      </c>
+      <c r="V81">
+        <v>54</v>
+      </c>
+      <c r="W81">
+        <v>1.5037590000000001</v>
+      </c>
+      <c r="X81">
+        <v>8</v>
+      </c>
+      <c r="Y81">
+        <v>2.0050129999999999</v>
+      </c>
+      <c r="Z81">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>28</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>80</v>
+      </c>
+      <c r="D82" t="s">
+        <v>31</v>
+      </c>
+      <c r="E82" t="s">
+        <v>39</v>
+      </c>
+      <c r="F82" t="s">
+        <v>33</v>
+      </c>
+      <c r="G82" t="s">
+        <v>68</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="K82">
+        <v>11</v>
+      </c>
+      <c r="L82">
+        <v>1.0909089999999999</v>
+      </c>
+      <c r="N82" t="s">
+        <v>53</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>13</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>79</v>
+      </c>
+      <c r="R82">
+        <v>12</v>
+      </c>
+      <c r="S82">
+        <v>1083.333333</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>28</v>
+      </c>
+      <c r="B83" t="s">
+        <v>29</v>
+      </c>
+      <c r="C83" t="s">
+        <v>80</v>
+      </c>
+      <c r="D83" t="s">
+        <v>31</v>
+      </c>
+      <c r="E83" t="s">
+        <v>40</v>
+      </c>
+      <c r="F83" t="s">
+        <v>33</v>
+      </c>
+      <c r="G83" t="s">
+        <v>68</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83">
+        <v>35</v>
+      </c>
+      <c r="L83">
+        <v>1.371429</v>
+      </c>
+      <c r="M83">
+        <v>11</v>
+      </c>
+      <c r="N83" t="s">
+        <v>53</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>11</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>79</v>
+      </c>
+      <c r="R83">
+        <v>48</v>
+      </c>
+      <c r="S83">
+        <v>229.16666699999999</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="V83">
+        <v>11</v>
+      </c>
+      <c r="W83">
+        <v>2.0833330000000001</v>
+      </c>
+      <c r="X83">
+        <v>1</v>
+      </c>
+      <c r="Y83">
+        <v>2.0833330000000001</v>
+      </c>
+      <c r="Z83">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" t="s">
+        <v>29</v>
+      </c>
+      <c r="C84" t="s">
+        <v>80</v>
+      </c>
+      <c r="D84" t="s">
+        <v>31</v>
+      </c>
+      <c r="E84" t="s">
+        <v>41</v>
+      </c>
+      <c r="F84" t="s">
+        <v>33</v>
+      </c>
+      <c r="G84" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84">
+        <v>5</v>
+      </c>
+      <c r="J84" t="s">
+        <v>36</v>
+      </c>
+      <c r="K84">
+        <v>348</v>
+      </c>
+      <c r="L84">
+        <v>1.3505750000000001</v>
+      </c>
+      <c r="M84">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="N84" t="s">
+        <v>53</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>358</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>79</v>
+      </c>
+      <c r="R84">
+        <v>470</v>
+      </c>
+      <c r="S84">
+        <v>761.70212800000002</v>
+      </c>
+      <c r="T84">
+        <v>5</v>
+      </c>
+      <c r="V84">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="W84">
+        <v>1.0638300000000001</v>
+      </c>
+      <c r="X84">
+        <v>6</v>
+      </c>
+      <c r="Y84">
+        <v>1.2765960000000001</v>
+      </c>
+      <c r="Z84">
+        <v>59.666666999999997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B85" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" t="s">
+        <v>80</v>
+      </c>
+      <c r="D85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" t="s">
+        <v>33</v>
+      </c>
+      <c r="G85" t="s">
+        <v>68</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85">
+        <v>179</v>
+      </c>
+      <c r="J85" t="s">
+        <v>36</v>
+      </c>
+      <c r="K85">
+        <v>3324</v>
+      </c>
+      <c r="L85">
+        <v>1.3417570000000001</v>
+      </c>
+      <c r="M85">
+        <v>29.74301676</v>
+      </c>
+      <c r="N85" t="s">
+        <v>53</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>5324</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>79</v>
+      </c>
+      <c r="R85">
+        <v>4460</v>
+      </c>
+      <c r="S85">
+        <v>1193.7219729999999</v>
+      </c>
+      <c r="T85">
+        <v>179</v>
+      </c>
+      <c r="V85">
+        <v>29.743016999999998</v>
+      </c>
+      <c r="W85">
+        <v>4.0134530000000002</v>
+      </c>
+      <c r="X85">
+        <v>181</v>
+      </c>
+      <c r="Y85">
+        <v>4.0582960000000003</v>
+      </c>
+      <c r="Z85">
+        <v>29.414365</v>
+      </c>
+    </row>
+    <row r="86" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>28</v>
+      </c>
+      <c r="B86" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" t="s">
+        <v>78</v>
+      </c>
+      <c r="D86" t="s">
+        <v>31</v>
+      </c>
+      <c r="E86" t="s">
+        <v>32</v>
+      </c>
+      <c r="F86" t="s">
+        <v>33</v>
+      </c>
+      <c r="G86" t="s">
+        <v>68</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86" t="s">
+        <v>36</v>
+      </c>
+      <c r="K86">
+        <v>1054</v>
+      </c>
+      <c r="L86">
+        <v>1.4497150000000001</v>
+      </c>
+      <c r="M86">
+        <v>44.809523810000002</v>
+      </c>
+      <c r="N86" t="s">
+        <v>53</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>1882</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>77</v>
+      </c>
+      <c r="R86">
+        <v>1528</v>
+      </c>
+      <c r="S86">
+        <v>1231.675393</v>
+      </c>
+      <c r="T86">
+        <v>42</v>
+      </c>
+      <c r="V86">
+        <v>44.809524000000003</v>
+      </c>
+      <c r="W86">
+        <v>2.748691</v>
+      </c>
+      <c r="X86">
+        <v>47</v>
+      </c>
+      <c r="Y86">
+        <v>3.0759159999999999</v>
+      </c>
+      <c r="Z86">
+        <v>40.042552999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>28</v>
+      </c>
+      <c r="B87" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87" t="s">
+        <v>31</v>
+      </c>
+      <c r="E87" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" t="s">
+        <v>56</v>
+      </c>
+      <c r="G87" t="s">
+        <v>68</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="N87" t="s">
+        <v>53</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>77</v>
+      </c>
+      <c r="R87">
+        <v>2</v>
+      </c>
+      <c r="S87">
+        <v>500</v>
+      </c>
+      <c r="X87">
+        <v>0</v>
+      </c>
+      <c r="Y87">
+        <v>0</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" t="s">
+        <v>78</v>
+      </c>
+      <c r="D88" t="s">
+        <v>31</v>
+      </c>
+      <c r="E88" t="s">
+        <v>39</v>
+      </c>
+      <c r="F88" t="s">
+        <v>33</v>
+      </c>
+      <c r="G88" t="s">
+        <v>68</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
+        <v>36</v>
+      </c>
+      <c r="K88">
+        <v>41</v>
+      </c>
+      <c r="L88">
+        <v>1.0243899999999999</v>
+      </c>
+      <c r="M88">
+        <v>22</v>
+      </c>
+      <c r="N88" t="s">
+        <v>53</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>22</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>77</v>
+      </c>
+      <c r="R88">
+        <v>42</v>
+      </c>
+      <c r="S88">
+        <v>523.80952400000001</v>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="V88">
+        <v>22</v>
+      </c>
+      <c r="W88">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="X88">
+        <v>1</v>
+      </c>
+      <c r="Y88">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z88">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>28</v>
+      </c>
+      <c r="B89" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" t="s">
+        <v>78</v>
+      </c>
+      <c r="D89" t="s">
+        <v>31</v>
+      </c>
+      <c r="E89" t="s">
+        <v>40</v>
+      </c>
+      <c r="F89" t="s">
+        <v>33</v>
+      </c>
+      <c r="G89" t="s">
+        <v>68</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89">
+        <v>64</v>
+      </c>
+      <c r="L89">
+        <v>1.359375</v>
+      </c>
+      <c r="N89" t="s">
+        <v>53</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>32</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>77</v>
+      </c>
+      <c r="R89">
+        <v>87</v>
+      </c>
+      <c r="S89">
+        <v>367.81609200000003</v>
+      </c>
+      <c r="X89">
+        <v>0</v>
+      </c>
+      <c r="Y89">
+        <v>0</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>28</v>
+      </c>
+      <c r="B90" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" t="s">
+        <v>78</v>
+      </c>
+      <c r="D90" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" t="s">
+        <v>41</v>
+      </c>
+      <c r="F90" t="s">
+        <v>33</v>
+      </c>
+      <c r="G90" t="s">
+        <v>68</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90">
+        <v>21</v>
+      </c>
+      <c r="J90" t="s">
+        <v>36</v>
+      </c>
+      <c r="K90">
+        <v>426</v>
+      </c>
+      <c r="L90">
+        <v>1.377934</v>
+      </c>
+      <c r="M90">
+        <v>40.571428570000002</v>
+      </c>
+      <c r="N90" t="s">
+        <v>53</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>852</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>77</v>
+      </c>
+      <c r="R90">
+        <v>587</v>
+      </c>
+      <c r="S90">
+        <v>1451.4480410000001</v>
+      </c>
+      <c r="T90">
+        <v>21</v>
+      </c>
+      <c r="V90">
+        <v>40.571429000000002</v>
+      </c>
+      <c r="W90">
+        <v>3.5775130000000002</v>
+      </c>
+      <c r="X90">
+        <v>23</v>
+      </c>
+      <c r="Y90">
+        <v>3.918228</v>
+      </c>
+      <c r="Z90">
+        <v>37.043478</v>
+      </c>
+    </row>
+    <row r="91" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>28</v>
+      </c>
+      <c r="B91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s">
+        <v>78</v>
+      </c>
+      <c r="D91" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" t="s">
+        <v>33</v>
+      </c>
+      <c r="G91" t="s">
+        <v>68</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91">
+        <v>94</v>
+      </c>
+      <c r="J91" t="s">
+        <v>36</v>
+      </c>
+      <c r="K91">
+        <v>1440</v>
+      </c>
+      <c r="L91">
+        <v>1.1819440000000001</v>
+      </c>
+      <c r="M91">
+        <v>41.861702129999998</v>
+      </c>
+      <c r="N91" t="s">
+        <v>53</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>3935</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>77</v>
+      </c>
+      <c r="R91">
+        <v>1702</v>
+      </c>
+      <c r="S91">
+        <v>2311.9858989999998</v>
+      </c>
+      <c r="T91">
+        <v>94</v>
+      </c>
+      <c r="V91">
+        <v>41.861702000000001</v>
+      </c>
+      <c r="W91">
+        <v>5.5229140000000001</v>
+      </c>
+      <c r="X91">
+        <v>101</v>
+      </c>
+      <c r="Y91">
+        <v>5.9341949999999999</v>
+      </c>
+      <c r="Z91">
+        <v>38.960396000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>28</v>
+      </c>
+      <c r="B92" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" t="s">
+        <v>78</v>
+      </c>
+      <c r="D92" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" t="s">
+        <v>56</v>
+      </c>
+      <c r="G92" t="s">
+        <v>68</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+      <c r="L92">
+        <v>1.5</v>
+      </c>
+      <c r="N92" t="s">
+        <v>53</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>3</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>77</v>
+      </c>
+      <c r="R92">
+        <v>3</v>
+      </c>
+      <c r="S92">
+        <v>1000</v>
+      </c>
+      <c r="X92">
+        <v>0</v>
+      </c>
+      <c r="Y92">
+        <v>0</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>28</v>
+      </c>
+      <c r="B93" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" t="s">
+        <v>76</v>
+      </c>
+      <c r="D93" t="s">
+        <v>31</v>
+      </c>
+      <c r="E93" t="s">
+        <v>32</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93" t="s">
+        <v>63</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93">
+        <v>9</v>
+      </c>
+      <c r="J93" t="s">
+        <v>36</v>
+      </c>
+      <c r="K93">
+        <v>278</v>
+      </c>
+      <c r="L93">
+        <v>1.2769779999999999</v>
+      </c>
+      <c r="M93">
+        <v>55.333333330000002</v>
+      </c>
+      <c r="N93" t="s">
+        <v>53</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>498</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>74</v>
+      </c>
+      <c r="R93">
+        <v>355</v>
+      </c>
+      <c r="S93">
+        <v>1402.8169009999999</v>
+      </c>
+      <c r="T93">
+        <v>9</v>
+      </c>
+      <c r="V93">
+        <v>55.333333000000003</v>
+      </c>
+      <c r="W93">
+        <v>2.5352109999999999</v>
+      </c>
+      <c r="X93">
+        <v>11</v>
+      </c>
+      <c r="Y93">
+        <v>3.098592</v>
+      </c>
+      <c r="Z93">
+        <v>45.272727000000003</v>
+      </c>
+      <c r="AA93">
+        <v>6</v>
+      </c>
+      <c r="AB93">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="94" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" t="s">
+        <v>76</v>
+      </c>
+      <c r="D94" t="s">
+        <v>31</v>
+      </c>
+      <c r="E94" t="s">
+        <v>39</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94" t="s">
+        <v>63</v>
+      </c>
+      <c r="H94" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="J94" t="s">
+        <v>36</v>
+      </c>
+      <c r="K94">
+        <v>28</v>
+      </c>
+      <c r="L94">
+        <v>1.142857</v>
+      </c>
+      <c r="M94">
+        <v>21</v>
+      </c>
+      <c r="N94" t="s">
+        <v>53</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>21</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>74</v>
+      </c>
+      <c r="R94">
+        <v>32</v>
+      </c>
+      <c r="S94">
+        <v>656.25</v>
+      </c>
+      <c r="T94">
+        <v>1</v>
+      </c>
+      <c r="V94">
+        <v>21</v>
+      </c>
+      <c r="W94">
+        <v>3.125</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
+        <v>3.125</v>
+      </c>
+      <c r="Z94">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="95" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>28</v>
+      </c>
+      <c r="B95" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" t="s">
+        <v>76</v>
+      </c>
+      <c r="D95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E95" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95" t="s">
+        <v>63</v>
+      </c>
+      <c r="H95" t="s">
+        <v>35</v>
+      </c>
+      <c r="K95">
+        <v>10</v>
+      </c>
+      <c r="L95">
+        <v>1</v>
+      </c>
+      <c r="N95" t="s">
+        <v>53</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>6</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>74</v>
+      </c>
+      <c r="R95">
+        <v>10</v>
+      </c>
+      <c r="S95">
+        <v>600</v>
+      </c>
+      <c r="X95">
+        <v>0</v>
+      </c>
+      <c r="Y95">
+        <v>0</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>28</v>
+      </c>
+      <c r="B96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" t="s">
+        <v>76</v>
+      </c>
+      <c r="D96" t="s">
+        <v>31</v>
+      </c>
+      <c r="E96" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96">
+        <v>11</v>
+      </c>
+      <c r="J96" t="s">
+        <v>36</v>
+      </c>
+      <c r="K96">
+        <v>393</v>
+      </c>
+      <c r="L96">
+        <v>1.1806620000000001</v>
+      </c>
+      <c r="M96">
+        <v>41.545454550000002</v>
+      </c>
+      <c r="N96" t="s">
+        <v>53</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>457</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>74</v>
+      </c>
+      <c r="R96">
+        <v>464</v>
+      </c>
+      <c r="S96">
+        <v>984.91379300000006</v>
+      </c>
+      <c r="T96">
+        <v>11</v>
+      </c>
+      <c r="V96">
+        <v>41.545454999999997</v>
+      </c>
+      <c r="W96">
+        <v>2.3706900000000002</v>
+      </c>
+      <c r="X96">
+        <v>12</v>
+      </c>
+      <c r="Y96">
+        <v>2.5862069999999999</v>
+      </c>
+      <c r="Z96">
+        <v>38.083333000000003</v>
+      </c>
+      <c r="AA96">
+        <v>7</v>
+      </c>
+      <c r="AB96">
+        <v>65.285713999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" t="s">
+        <v>29</v>
+      </c>
+      <c r="C97" t="s">
+        <v>76</v>
+      </c>
+      <c r="D97" t="s">
+        <v>31</v>
+      </c>
+      <c r="E97" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97" t="s">
+        <v>63</v>
+      </c>
+      <c r="H97" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97">
+        <v>109</v>
+      </c>
+      <c r="J97" t="s">
+        <v>36</v>
+      </c>
+      <c r="K97">
+        <v>2730</v>
+      </c>
+      <c r="L97">
+        <v>1.219414</v>
+      </c>
+      <c r="M97">
+        <v>52.990825690000001</v>
+      </c>
+      <c r="N97" t="s">
+        <v>53</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>5776</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>74</v>
+      </c>
+      <c r="R97">
+        <v>3329</v>
+      </c>
+      <c r="S97">
+        <v>1735.055572</v>
+      </c>
+      <c r="T97">
+        <v>109</v>
+      </c>
+      <c r="V97">
+        <v>52.990825999999998</v>
+      </c>
+      <c r="W97">
+        <v>3.274257</v>
+      </c>
+      <c r="X97">
+        <v>115</v>
+      </c>
+      <c r="Y97">
+        <v>3.454491</v>
+      </c>
+      <c r="Z97">
+        <v>50.226087</v>
+      </c>
+      <c r="AA97">
+        <v>48</v>
+      </c>
+      <c r="AB97">
+        <v>120.333333</v>
+      </c>
+    </row>
+    <row r="98" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>28</v>
+      </c>
+      <c r="B98" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" t="s">
+        <v>75</v>
+      </c>
+      <c r="D98" t="s">
+        <v>31</v>
+      </c>
+      <c r="E98" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98" t="s">
+        <v>63</v>
+      </c>
+      <c r="H98" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98">
+        <v>14</v>
+      </c>
+      <c r="J98" t="s">
+        <v>36</v>
+      </c>
+      <c r="K98">
+        <v>568</v>
+      </c>
+      <c r="L98">
+        <v>1.431338</v>
+      </c>
+      <c r="M98">
+        <v>52.571428570000002</v>
+      </c>
+      <c r="N98" t="s">
+        <v>53</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>736</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>74</v>
+      </c>
+      <c r="R98">
+        <v>813</v>
+      </c>
+      <c r="S98">
+        <v>905.28905299999997</v>
+      </c>
+      <c r="T98">
+        <v>14</v>
+      </c>
+      <c r="V98">
+        <v>52.571429000000002</v>
+      </c>
+      <c r="W98">
+        <v>1.7220169999999999</v>
+      </c>
+      <c r="X98">
+        <v>11</v>
+      </c>
+      <c r="Y98">
+        <v>1.3530139999999999</v>
+      </c>
+      <c r="Z98">
+        <v>66.909091000000004</v>
+      </c>
+      <c r="AA98">
+        <v>11</v>
+      </c>
+      <c r="AB98">
+        <v>66.909091000000004</v>
+      </c>
+    </row>
+    <row r="99" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>28</v>
+      </c>
+      <c r="B99" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" t="s">
+        <v>75</v>
+      </c>
+      <c r="D99" t="s">
+        <v>31</v>
+      </c>
+      <c r="E99" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99" t="s">
+        <v>63</v>
+      </c>
+      <c r="H99" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99">
+        <v>2</v>
+      </c>
+      <c r="J99" t="s">
+        <v>36</v>
+      </c>
+      <c r="K99">
+        <v>34</v>
+      </c>
+      <c r="L99">
+        <v>1.176471</v>
+      </c>
+      <c r="M99">
+        <v>9.5</v>
+      </c>
+      <c r="N99" t="s">
+        <v>53</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>19</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>74</v>
+      </c>
+      <c r="R99">
+        <v>40</v>
+      </c>
+      <c r="S99">
+        <v>475</v>
+      </c>
+      <c r="T99">
+        <v>2</v>
+      </c>
+      <c r="V99">
+        <v>9.5</v>
+      </c>
+      <c r="W99">
+        <v>5</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99">
+        <v>2.5</v>
+      </c>
+      <c r="Z99">
+        <v>19</v>
+      </c>
+      <c r="AA99">
+        <v>1</v>
+      </c>
+      <c r="AB99">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>28</v>
+      </c>
+      <c r="B100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" t="s">
+        <v>75</v>
+      </c>
+      <c r="D100" t="s">
+        <v>31</v>
+      </c>
+      <c r="E100" t="s">
+        <v>40</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100" t="s">
+        <v>63</v>
+      </c>
+      <c r="H100" t="s">
+        <v>35</v>
+      </c>
+      <c r="K100">
+        <v>70</v>
+      </c>
+      <c r="L100">
+        <v>1.2285710000000001</v>
+      </c>
+      <c r="N100" t="s">
+        <v>53</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>20</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>74</v>
+      </c>
+      <c r="R100">
+        <v>86</v>
+      </c>
+      <c r="S100">
+        <v>232.55814000000001</v>
+      </c>
+      <c r="X100">
+        <v>0</v>
+      </c>
+      <c r="Y100">
+        <v>0</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" t="s">
+        <v>75</v>
+      </c>
+      <c r="D101" t="s">
+        <v>31</v>
+      </c>
+      <c r="E101" t="s">
+        <v>41</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101" t="s">
+        <v>63</v>
+      </c>
+      <c r="H101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I101">
+        <v>6</v>
+      </c>
+      <c r="J101" t="s">
+        <v>36</v>
+      </c>
+      <c r="K101">
+        <v>298</v>
+      </c>
+      <c r="L101">
+        <v>1.3389260000000001</v>
+      </c>
+      <c r="M101">
+        <v>58.666666669999998</v>
+      </c>
+      <c r="N101" t="s">
+        <v>53</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>352</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>74</v>
+      </c>
+      <c r="R101">
+        <v>399</v>
+      </c>
+      <c r="S101">
+        <v>882.20551399999999</v>
+      </c>
+      <c r="T101">
+        <v>6</v>
+      </c>
+      <c r="V101">
+        <v>58.666666999999997</v>
+      </c>
+      <c r="W101">
+        <v>1.5037590000000001</v>
+      </c>
+      <c r="X101">
+        <v>7</v>
+      </c>
+      <c r="Y101">
+        <v>1.754386</v>
+      </c>
+      <c r="Z101">
+        <v>50.285713999999999</v>
+      </c>
+      <c r="AA101">
+        <v>6</v>
+      </c>
+      <c r="AB101">
+        <v>58.666666999999997</v>
+      </c>
+    </row>
+    <row r="102" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>28</v>
+      </c>
+      <c r="B102" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" t="s">
+        <v>75</v>
+      </c>
+      <c r="D102" t="s">
+        <v>31</v>
+      </c>
+      <c r="E102" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102" t="s">
+        <v>63</v>
+      </c>
+      <c r="H102" t="s">
+        <v>35</v>
+      </c>
+      <c r="I102">
+        <v>142</v>
+      </c>
+      <c r="J102" t="s">
+        <v>36</v>
+      </c>
+      <c r="K102">
+        <v>3197</v>
+      </c>
+      <c r="L102">
+        <v>1.1786049999999999</v>
+      </c>
+      <c r="M102">
+        <v>38.535211269999998</v>
+      </c>
+      <c r="N102" t="s">
+        <v>53</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>5472</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>74</v>
+      </c>
+      <c r="R102">
+        <v>3768</v>
+      </c>
+      <c r="S102">
+        <v>1452.2292990000001</v>
+      </c>
+      <c r="T102">
+        <v>142</v>
+      </c>
+      <c r="V102">
+        <v>38.535210999999997</v>
+      </c>
+      <c r="W102">
+        <v>3.7685770000000001</v>
+      </c>
+      <c r="X102">
+        <v>149</v>
+      </c>
+      <c r="Y102">
+        <v>3.9543520000000001</v>
+      </c>
+      <c r="Z102">
+        <v>36.724831999999999</v>
+      </c>
+      <c r="AA102">
+        <v>120</v>
+      </c>
+      <c r="AB102">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>28</v>
+      </c>
+      <c r="B103" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" t="s">
+        <v>73</v>
+      </c>
+      <c r="D103" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" t="s">
+        <v>32</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103" t="s">
+        <v>68</v>
+      </c>
+      <c r="H103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I103">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s">
+        <v>36</v>
+      </c>
+      <c r="K103">
+        <v>783</v>
+      </c>
+      <c r="L103">
+        <v>1.2669220000000001</v>
+      </c>
+      <c r="M103">
+        <v>42.631578949999998</v>
+      </c>
+      <c r="N103" t="s">
+        <v>53</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>810</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>70</v>
+      </c>
+      <c r="R103">
+        <v>992</v>
+      </c>
+      <c r="S103">
+        <v>816.53225799999996</v>
+      </c>
+      <c r="T103">
+        <v>19</v>
+      </c>
+      <c r="V103">
+        <v>42.631579000000002</v>
+      </c>
+      <c r="W103">
+        <v>1.9153230000000001</v>
+      </c>
+      <c r="X103">
+        <v>21</v>
+      </c>
+      <c r="Y103">
+        <v>2.1169349999999998</v>
+      </c>
+      <c r="Z103">
+        <v>38.571429000000002</v>
+      </c>
+      <c r="AA103">
+        <v>16</v>
+      </c>
+      <c r="AB103">
+        <v>50.625</v>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>28</v>
+      </c>
+      <c r="B104" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" t="s">
+        <v>73</v>
+      </c>
+      <c r="D104" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" t="s">
+        <v>32</v>
+      </c>
+      <c r="F104" t="s">
+        <v>56</v>
+      </c>
+      <c r="G104" t="s">
+        <v>68</v>
+      </c>
+      <c r="H104" t="s">
+        <v>35</v>
+      </c>
+      <c r="K104">
+        <v>1</v>
+      </c>
+      <c r="L104">
+        <v>1</v>
+      </c>
+      <c r="N104" t="s">
+        <v>53</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>70</v>
+      </c>
+      <c r="R104">
+        <v>1</v>
+      </c>
+      <c r="S104">
+        <v>1000</v>
+      </c>
+      <c r="X104">
+        <v>0</v>
+      </c>
+      <c r="Y104">
+        <v>0</v>
+      </c>
+      <c r="Z104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>28</v>
+      </c>
+      <c r="B105" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" t="s">
+        <v>73</v>
+      </c>
+      <c r="D105" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" t="s">
+        <v>39</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105" t="s">
+        <v>68</v>
+      </c>
+      <c r="H105" t="s">
+        <v>35</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105" t="s">
+        <v>36</v>
+      </c>
+      <c r="K105">
+        <v>66</v>
+      </c>
+      <c r="L105">
+        <v>1.106061</v>
+      </c>
+      <c r="M105">
+        <v>57</v>
+      </c>
+      <c r="N105" t="s">
+        <v>53</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>57</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>70</v>
+      </c>
+      <c r="R105">
+        <v>73</v>
+      </c>
+      <c r="S105">
+        <v>780.82191799999998</v>
+      </c>
+      <c r="T105">
+        <v>1</v>
+      </c>
+      <c r="V105">
+        <v>57</v>
+      </c>
+      <c r="W105">
+        <v>1.3698630000000001</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>1.3698630000000001</v>
+      </c>
+      <c r="Z105">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="106" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>28</v>
+      </c>
+      <c r="B106" t="s">
+        <v>29</v>
+      </c>
+      <c r="C106" t="s">
+        <v>73</v>
+      </c>
+      <c r="D106" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" t="s">
+        <v>40</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106" t="s">
+        <v>68</v>
+      </c>
+      <c r="H106" t="s">
+        <v>35</v>
+      </c>
+      <c r="K106">
+        <v>25</v>
+      </c>
+      <c r="L106">
+        <v>1.08</v>
+      </c>
+      <c r="N106" t="s">
+        <v>53</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>7</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>70</v>
+      </c>
+      <c r="R106">
+        <v>27</v>
+      </c>
+      <c r="S106">
+        <v>259.25925899999999</v>
+      </c>
+      <c r="X106">
+        <v>0</v>
+      </c>
+      <c r="Y106">
+        <v>0</v>
+      </c>
+      <c r="Z106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" t="s">
+        <v>29</v>
+      </c>
+      <c r="C107" t="s">
+        <v>73</v>
+      </c>
+      <c r="D107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" t="s">
+        <v>41</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107" t="s">
+        <v>68</v>
+      </c>
+      <c r="H107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I107">
+        <v>52</v>
+      </c>
+      <c r="J107" t="s">
+        <v>36</v>
+      </c>
+      <c r="K107">
+        <v>969</v>
+      </c>
+      <c r="L107">
+        <v>1.4117649999999999</v>
+      </c>
+      <c r="M107">
+        <v>26.92307692</v>
+      </c>
+      <c r="N107" t="s">
+        <v>53</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>1400</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>70</v>
+      </c>
+      <c r="R107">
+        <v>1368</v>
+      </c>
+      <c r="S107">
+        <v>1023.391813</v>
+      </c>
+      <c r="T107">
+        <v>52</v>
+      </c>
+      <c r="V107">
+        <v>26.923076999999999</v>
+      </c>
+      <c r="W107">
+        <v>3.8011699999999999</v>
+      </c>
+      <c r="X107">
+        <v>58</v>
+      </c>
+      <c r="Y107">
+        <v>4.2397660000000004</v>
+      </c>
+      <c r="Z107">
+        <v>24.137930999999998</v>
+      </c>
+      <c r="AA107">
+        <v>48</v>
+      </c>
+      <c r="AB107">
+        <v>29.166667</v>
+      </c>
+    </row>
+    <row r="108" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>28</v>
+      </c>
+      <c r="B108" t="s">
+        <v>29</v>
+      </c>
+      <c r="C108" t="s">
+        <v>73</v>
+      </c>
+      <c r="D108" t="s">
+        <v>31</v>
+      </c>
+      <c r="E108" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108" t="s">
+        <v>68</v>
+      </c>
+      <c r="H108" t="s">
+        <v>35</v>
+      </c>
+      <c r="I108">
+        <v>84</v>
+      </c>
+      <c r="J108" t="s">
+        <v>36</v>
+      </c>
+      <c r="K108">
+        <v>2328</v>
+      </c>
+      <c r="L108">
+        <v>1.293814</v>
+      </c>
+      <c r="M108">
+        <v>48.119047620000003</v>
+      </c>
+      <c r="N108" t="s">
+        <v>53</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>4042</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>70</v>
+      </c>
+      <c r="R108">
+        <v>3012</v>
+      </c>
+      <c r="S108">
+        <v>1341.965471</v>
+      </c>
+      <c r="T108">
+        <v>84</v>
+      </c>
+      <c r="V108">
+        <v>48.119047999999999</v>
+      </c>
+      <c r="W108">
+        <v>2.7888449999999998</v>
+      </c>
+      <c r="X108">
+        <v>100</v>
+      </c>
+      <c r="Y108">
+        <v>3.3200530000000001</v>
+      </c>
+      <c r="Z108">
+        <v>40.42</v>
+      </c>
+      <c r="AA108">
+        <v>63</v>
+      </c>
+      <c r="AB108">
+        <v>64.158730000000006</v>
+      </c>
+    </row>
+    <row r="109" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>28</v>
+      </c>
+      <c r="B109" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" t="s">
+        <v>72</v>
+      </c>
+      <c r="D109" t="s">
+        <v>31</v>
+      </c>
+      <c r="E109" t="s">
+        <v>32</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109" t="s">
+        <v>63</v>
+      </c>
+      <c r="H109" t="s">
+        <v>35</v>
+      </c>
+      <c r="I109">
+        <v>37</v>
+      </c>
+      <c r="J109" t="s">
+        <v>36</v>
+      </c>
+      <c r="K109">
+        <v>1316</v>
+      </c>
+      <c r="L109">
+        <v>1.3305469999999999</v>
+      </c>
+      <c r="M109">
+        <v>36.675675679999998</v>
+      </c>
+      <c r="N109" t="s">
+        <v>53</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>1357</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>29</v>
+      </c>
+      <c r="R109">
+        <v>1751</v>
+      </c>
+      <c r="S109">
+        <v>774.98572200000001</v>
+      </c>
+      <c r="T109">
+        <v>37</v>
+      </c>
+      <c r="V109">
+        <v>36.675676000000003</v>
+      </c>
+      <c r="W109">
+        <v>2.1130779999999998</v>
+      </c>
+      <c r="X109">
+        <v>45</v>
+      </c>
+      <c r="Y109">
+        <v>2.56996</v>
+      </c>
+      <c r="Z109">
+        <v>30.155556000000001</v>
+      </c>
+      <c r="AA109">
+        <v>30</v>
+      </c>
+      <c r="AB109">
+        <v>45.233333000000002</v>
+      </c>
+    </row>
+    <row r="110" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>72</v>
+      </c>
+      <c r="D110" t="s">
+        <v>31</v>
+      </c>
+      <c r="E110" t="s">
+        <v>32</v>
+      </c>
+      <c r="F110" t="s">
+        <v>56</v>
+      </c>
+      <c r="G110" t="s">
+        <v>63</v>
+      </c>
+      <c r="H110" t="s">
+        <v>35</v>
+      </c>
+      <c r="K110">
+        <v>2</v>
+      </c>
+      <c r="L110">
+        <v>1</v>
+      </c>
+      <c r="N110" t="s">
+        <v>53</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>2</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>29</v>
+      </c>
+      <c r="R110">
+        <v>2</v>
+      </c>
+      <c r="S110">
+        <v>1000</v>
+      </c>
+      <c r="X110">
+        <v>0</v>
+      </c>
+      <c r="Y110">
+        <v>0</v>
+      </c>
+      <c r="Z110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>28</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" t="s">
+        <v>72</v>
+      </c>
+      <c r="D111" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111" t="s">
+        <v>63</v>
+      </c>
+      <c r="H111" t="s">
+        <v>35</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="J111" t="s">
+        <v>36</v>
+      </c>
+      <c r="K111">
+        <v>50</v>
+      </c>
+      <c r="L111">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M111">
+        <v>17</v>
+      </c>
+      <c r="N111" t="s">
+        <v>53</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>34</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>29</v>
+      </c>
+      <c r="R111">
+        <v>58</v>
+      </c>
+      <c r="S111">
+        <v>586.20689700000003</v>
+      </c>
+      <c r="T111">
+        <v>2</v>
+      </c>
+      <c r="V111">
+        <v>17</v>
+      </c>
+      <c r="W111">
+        <v>3.4482759999999999</v>
+      </c>
+      <c r="X111">
+        <v>4</v>
+      </c>
+      <c r="Y111">
+        <v>6.8965519999999998</v>
+      </c>
+      <c r="Z111">
+        <v>8.5</v>
+      </c>
+      <c r="AA111">
+        <v>1</v>
+      </c>
+      <c r="AB111">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>28</v>
+      </c>
+      <c r="B112" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" t="s">
+        <v>72</v>
+      </c>
+      <c r="D112" t="s">
+        <v>31</v>
+      </c>
+      <c r="E112" t="s">
+        <v>40</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112" t="s">
+        <v>63</v>
+      </c>
+      <c r="H112" t="s">
+        <v>35</v>
+      </c>
+      <c r="I112">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>36</v>
+      </c>
+      <c r="K112">
+        <v>40</v>
+      </c>
+      <c r="L112">
+        <v>1.05</v>
+      </c>
+      <c r="M112">
+        <v>11</v>
+      </c>
+      <c r="N112" t="s">
+        <v>53</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>11</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>29</v>
+      </c>
+      <c r="R112">
+        <v>42</v>
+      </c>
+      <c r="S112">
+        <v>261.90476200000001</v>
+      </c>
+      <c r="T112">
+        <v>1</v>
+      </c>
+      <c r="V112">
+        <v>11</v>
+      </c>
+      <c r="W112">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="X112">
+        <v>1</v>
+      </c>
+      <c r="Y112">
+        <v>2.3809520000000002</v>
+      </c>
+      <c r="Z112">
+        <v>11</v>
+      </c>
+      <c r="AA112">
+        <v>1</v>
+      </c>
+      <c r="AB112">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>72</v>
+      </c>
+      <c r="D113" t="s">
+        <v>31</v>
+      </c>
+      <c r="E113" t="s">
+        <v>41</v>
+      </c>
+      <c r="F113" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113" t="s">
+        <v>63</v>
+      </c>
+      <c r="H113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I113">
+        <v>15</v>
+      </c>
+      <c r="J113" t="s">
+        <v>36</v>
+      </c>
+      <c r="K113">
+        <v>668</v>
+      </c>
+      <c r="L113">
+        <v>1.193114</v>
+      </c>
+      <c r="M113">
+        <v>42.066666669999996</v>
+      </c>
+      <c r="N113" t="s">
+        <v>53</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>631</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>29</v>
+      </c>
+      <c r="R113">
+        <v>797</v>
+      </c>
+      <c r="S113">
+        <v>791.71894599999996</v>
+      </c>
+      <c r="T113">
+        <v>15</v>
+      </c>
+      <c r="V113">
+        <v>42.066667000000002</v>
+      </c>
+      <c r="W113">
+        <v>1.882058</v>
+      </c>
+      <c r="X113">
+        <v>15</v>
+      </c>
+      <c r="Y113">
+        <v>1.882058</v>
+      </c>
+      <c r="Z113">
+        <v>42.066667000000002</v>
+      </c>
+      <c r="AA113">
+        <v>15</v>
+      </c>
+      <c r="AB113">
+        <v>42.066667000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>28</v>
+      </c>
+      <c r="B114" t="s">
+        <v>29</v>
+      </c>
+      <c r="C114" t="s">
+        <v>72</v>
+      </c>
+      <c r="D114" t="s">
+        <v>31</v>
+      </c>
+      <c r="E114" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114" t="s">
+        <v>63</v>
+      </c>
+      <c r="H114" t="s">
+        <v>35</v>
+      </c>
+      <c r="I114">
+        <v>49</v>
+      </c>
+      <c r="J114" t="s">
+        <v>36</v>
+      </c>
+      <c r="K114">
+        <v>1483</v>
+      </c>
+      <c r="L114">
+        <v>1.271072</v>
+      </c>
+      <c r="M114">
+        <v>40.714285709999999</v>
+      </c>
+      <c r="N114" t="s">
+        <v>53</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>1995</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>29</v>
+      </c>
+      <c r="R114">
+        <v>1885</v>
+      </c>
+      <c r="S114">
+        <v>1058.355438</v>
+      </c>
+      <c r="T114">
+        <v>49</v>
+      </c>
+      <c r="V114">
+        <v>40.714286000000001</v>
+      </c>
+      <c r="W114">
+        <v>2.5994700000000002</v>
+      </c>
+      <c r="X114">
+        <v>60</v>
+      </c>
+      <c r="Y114">
+        <v>3.1830240000000001</v>
+      </c>
+      <c r="Z114">
+        <v>33.25</v>
+      </c>
+      <c r="AA114">
+        <v>44</v>
+      </c>
+      <c r="AB114">
+        <v>45.340909000000003</v>
+      </c>
+    </row>
+    <row r="115" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" t="s">
+        <v>71</v>
+      </c>
+      <c r="D115" t="s">
+        <v>31</v>
+      </c>
+      <c r="E115" t="s">
+        <v>32</v>
+      </c>
+      <c r="F115" t="s">
+        <v>33</v>
+      </c>
+      <c r="G115" t="s">
+        <v>68</v>
+      </c>
+      <c r="H115" t="s">
+        <v>35</v>
+      </c>
+      <c r="I115">
+        <v>6</v>
+      </c>
+      <c r="J115" t="s">
+        <v>36</v>
+      </c>
+      <c r="K115">
+        <v>240</v>
+      </c>
+      <c r="L115">
+        <v>1.3458330000000001</v>
+      </c>
+      <c r="M115">
+        <v>88</v>
+      </c>
+      <c r="N115" t="s">
+        <v>53</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>528</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>70</v>
+      </c>
+      <c r="R115">
+        <v>323</v>
+      </c>
+      <c r="S115">
+        <v>1634.674923</v>
+      </c>
+      <c r="T115">
+        <v>6</v>
+      </c>
+      <c r="V115">
+        <v>88</v>
+      </c>
+      <c r="W115">
+        <v>1.857585</v>
+      </c>
+      <c r="X115">
+        <v>7</v>
+      </c>
+      <c r="Y115">
+        <v>2.1671830000000001</v>
+      </c>
+      <c r="Z115">
+        <v>75.428571000000005</v>
+      </c>
+      <c r="AA115">
+        <v>5</v>
+      </c>
+      <c r="AB115">
+        <v>105.6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>28</v>
+      </c>
+      <c r="B116" t="s">
+        <v>29</v>
+      </c>
+      <c r="C116" t="s">
+        <v>71</v>
+      </c>
+      <c r="D116" t="s">
+        <v>31</v>
+      </c>
+      <c r="E116" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G116" t="s">
+        <v>68</v>
+      </c>
+      <c r="H116" t="s">
+        <v>35</v>
+      </c>
+      <c r="K116">
+        <v>30</v>
+      </c>
+      <c r="L116">
+        <v>1.066667</v>
+      </c>
+      <c r="N116" t="s">
+        <v>53</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>24</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>70</v>
+      </c>
+      <c r="R116">
+        <v>32</v>
+      </c>
+      <c r="S116">
+        <v>750</v>
+      </c>
+      <c r="X116">
+        <v>0</v>
+      </c>
+      <c r="Y116">
+        <v>0</v>
+      </c>
+      <c r="Z116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>28</v>
+      </c>
+      <c r="B117" t="s">
+        <v>29</v>
+      </c>
+      <c r="C117" t="s">
+        <v>71</v>
+      </c>
+      <c r="D117" t="s">
+        <v>31</v>
+      </c>
+      <c r="E117" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" t="s">
+        <v>33</v>
+      </c>
+      <c r="G117" t="s">
+        <v>68</v>
+      </c>
+      <c r="H117" t="s">
+        <v>35</v>
+      </c>
+      <c r="K117">
+        <v>6</v>
+      </c>
+      <c r="L117">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N117" t="s">
+        <v>53</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>8</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>70</v>
+      </c>
+      <c r="R117">
+        <v>7</v>
+      </c>
+      <c r="S117">
+        <v>1142.857143</v>
+      </c>
+      <c r="X117">
+        <v>0</v>
+      </c>
+      <c r="Y117">
+        <v>0</v>
+      </c>
+      <c r="Z117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>28</v>
+      </c>
+      <c r="B118" t="s">
+        <v>29</v>
+      </c>
+      <c r="C118" t="s">
+        <v>71</v>
+      </c>
+      <c r="D118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E118" t="s">
+        <v>41</v>
+      </c>
+      <c r="F118" t="s">
+        <v>33</v>
+      </c>
+      <c r="G118" t="s">
+        <v>68</v>
+      </c>
+      <c r="H118" t="s">
+        <v>35</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="J118" t="s">
+        <v>36</v>
+      </c>
+      <c r="K118">
+        <v>131</v>
+      </c>
+      <c r="L118">
+        <v>1.221374</v>
+      </c>
+      <c r="M118">
+        <v>141</v>
+      </c>
+      <c r="N118" t="s">
+        <v>53</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>141</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>70</v>
+      </c>
+      <c r="R118">
+        <v>160</v>
+      </c>
+      <c r="S118">
+        <v>881.25</v>
+      </c>
+      <c r="T118">
+        <v>1</v>
+      </c>
+      <c r="V118">
+        <v>141</v>
+      </c>
+      <c r="W118">
+        <v>0.625</v>
+      </c>
+      <c r="X118">
+        <v>2</v>
+      </c>
+      <c r="Y118">
+        <v>1.25</v>
+      </c>
+      <c r="Z118">
+        <v>70.5</v>
+      </c>
+      <c r="AA118">
+        <v>1</v>
+      </c>
+      <c r="AB118">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="119" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>28</v>
+      </c>
+      <c r="B119" t="s">
+        <v>29</v>
+      </c>
+      <c r="C119" t="s">
+        <v>71</v>
+      </c>
+      <c r="D119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E119" t="s">
+        <v>42</v>
+      </c>
+      <c r="F119" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119" t="s">
+        <v>68</v>
+      </c>
+      <c r="H119" t="s">
+        <v>35</v>
+      </c>
+      <c r="I119">
+        <v>90</v>
+      </c>
+      <c r="J119" t="s">
+        <v>36</v>
+      </c>
+      <c r="K119">
+        <v>6048</v>
+      </c>
+      <c r="L119">
+        <v>1.5636570000000001</v>
+      </c>
+      <c r="M119">
+        <v>61.5</v>
+      </c>
+      <c r="N119" t="s">
+        <v>53</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>5535</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>70</v>
+      </c>
+      <c r="R119">
+        <v>9457</v>
+      </c>
+      <c r="S119">
+        <v>585.28074400000003</v>
+      </c>
+      <c r="T119">
+        <v>90</v>
+      </c>
+      <c r="V119">
+        <v>61.5</v>
+      </c>
+      <c r="W119">
+        <v>0.95167599999999997</v>
+      </c>
+      <c r="X119">
+        <v>97</v>
+      </c>
+      <c r="Y119">
+        <v>1.025695</v>
+      </c>
+      <c r="Z119">
+        <v>57.061855999999999</v>
+      </c>
+      <c r="AA119">
+        <v>63</v>
+      </c>
+      <c r="AB119">
+        <v>87.857142999999994</v>
+      </c>
+    </row>
+    <row r="120" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120" t="s">
+        <v>29</v>
+      </c>
+      <c r="C120" t="s">
+        <v>69</v>
+      </c>
+      <c r="D120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" t="s">
+        <v>32</v>
+      </c>
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="G120" t="s">
+        <v>68</v>
+      </c>
+      <c r="H120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I120">
+        <v>4</v>
+      </c>
+      <c r="J120" t="s">
+        <v>36</v>
+      </c>
+      <c r="K120">
+        <v>182</v>
+      </c>
+      <c r="L120">
+        <v>1.461538</v>
+      </c>
+      <c r="M120">
+        <v>66</v>
+      </c>
+      <c r="N120" t="s">
+        <v>53</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>264</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>67</v>
+      </c>
+      <c r="R120">
+        <v>266</v>
+      </c>
+      <c r="S120">
+        <v>992.48120300000005</v>
+      </c>
+      <c r="T120">
+        <v>4</v>
+      </c>
+      <c r="V120">
+        <v>66</v>
+      </c>
+      <c r="W120">
+        <v>1.5037590000000001</v>
+      </c>
+      <c r="X120">
+        <v>5</v>
+      </c>
+      <c r="Y120">
+        <v>1.879699</v>
+      </c>
+      <c r="Z120">
+        <v>52.8</v>
+      </c>
+      <c r="AA120">
+        <v>3</v>
+      </c>
+      <c r="AB120">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="121" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>28</v>
+      </c>
+      <c r="B121" t="s">
+        <v>29</v>
+      </c>
+      <c r="C121" t="s">
+        <v>69</v>
+      </c>
+      <c r="D121" t="s">
+        <v>31</v>
+      </c>
+      <c r="E121" t="s">
+        <v>39</v>
+      </c>
+      <c r="F121" t="s">
+        <v>33</v>
+      </c>
+      <c r="G121" t="s">
+        <v>68</v>
+      </c>
+      <c r="H121" t="s">
+        <v>35</v>
+      </c>
+      <c r="K121">
+        <v>32</v>
+      </c>
+      <c r="L121">
+        <v>1.5625</v>
+      </c>
+      <c r="N121" t="s">
+        <v>53</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>19</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>67</v>
+      </c>
+      <c r="R121">
+        <v>50</v>
+      </c>
+      <c r="S121">
+        <v>380</v>
+      </c>
+      <c r="X121">
+        <v>0</v>
+      </c>
+      <c r="Y121">
+        <v>0</v>
+      </c>
+      <c r="Z121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>29</v>
+      </c>
+      <c r="C122" t="s">
+        <v>69</v>
+      </c>
+      <c r="D122" t="s">
+        <v>31</v>
+      </c>
+      <c r="E122" t="s">
+        <v>40</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122" t="s">
+        <v>68</v>
+      </c>
+      <c r="H122" t="s">
+        <v>35</v>
+      </c>
+      <c r="K122">
+        <v>7</v>
+      </c>
+      <c r="L122">
+        <v>2.8571430000000002</v>
+      </c>
+      <c r="N122" t="s">
+        <v>53</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>3</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>67</v>
+      </c>
+      <c r="R122">
+        <v>20</v>
+      </c>
+      <c r="S122">
+        <v>150</v>
+      </c>
+      <c r="X122">
+        <v>0</v>
+      </c>
+      <c r="Y122">
+        <v>0</v>
+      </c>
+      <c r="Z122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>28</v>
+      </c>
+      <c r="B123" t="s">
+        <v>29</v>
+      </c>
+      <c r="C123" t="s">
+        <v>69</v>
+      </c>
+      <c r="D123" t="s">
+        <v>31</v>
+      </c>
+      <c r="E123" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123" t="s">
+        <v>68</v>
+      </c>
+      <c r="H123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>36</v>
+      </c>
+      <c r="K123">
+        <v>136</v>
+      </c>
+      <c r="L123">
+        <v>1.2279409999999999</v>
+      </c>
+      <c r="M123">
+        <v>118</v>
+      </c>
+      <c r="N123" t="s">
+        <v>53</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>118</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>67</v>
+      </c>
+      <c r="R123">
+        <v>167</v>
+      </c>
+      <c r="S123">
+        <v>706.58682599999997</v>
+      </c>
+      <c r="T123">
+        <v>1</v>
+      </c>
+      <c r="V123">
+        <v>118</v>
+      </c>
+      <c r="W123">
+        <v>0.59880199999999995</v>
+      </c>
+      <c r="X123">
+        <v>2</v>
+      </c>
+      <c r="Y123">
+        <v>1.197605</v>
+      </c>
+      <c r="Z123">
+        <v>59</v>
+      </c>
+      <c r="AA123">
+        <v>1</v>
+      </c>
+      <c r="AB123">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>28</v>
+      </c>
+      <c r="B124" t="s">
+        <v>29</v>
+      </c>
+      <c r="C124" t="s">
+        <v>69</v>
+      </c>
+      <c r="D124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" t="s">
+        <v>33</v>
+      </c>
+      <c r="G124" t="s">
+        <v>68</v>
+      </c>
+      <c r="H124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I124">
+        <v>128</v>
+      </c>
+      <c r="J124" t="s">
+        <v>36</v>
+      </c>
+      <c r="K124">
+        <v>4806</v>
+      </c>
+      <c r="L124">
+        <v>1.558052</v>
+      </c>
+      <c r="M124">
+        <v>45.8125</v>
+      </c>
+      <c r="N124" t="s">
+        <v>53</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>5864</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>67</v>
+      </c>
+      <c r="R124">
+        <v>7488</v>
+      </c>
+      <c r="S124">
+        <v>783.11965799999996</v>
+      </c>
+      <c r="T124">
+        <v>128</v>
+      </c>
+      <c r="V124">
+        <v>45.8125</v>
+      </c>
+      <c r="W124">
+        <v>1.7094020000000001</v>
+      </c>
+      <c r="X124">
+        <v>134</v>
+      </c>
+      <c r="Y124">
+        <v>1.7895300000000001</v>
+      </c>
+      <c r="Z124">
+        <v>43.761194000000003</v>
+      </c>
+      <c r="AA124">
+        <v>86</v>
+      </c>
+      <c r="AB124">
+        <v>68.186047000000002</v>
+      </c>
+    </row>
+    <row r="125" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>28</v>
+      </c>
+      <c r="B125" t="s">
+        <v>29</v>
+      </c>
+      <c r="C125" t="s">
+        <v>66</v>
+      </c>
+      <c r="D125" t="s">
+        <v>31</v>
+      </c>
+      <c r="E125" t="s">
+        <v>32</v>
+      </c>
+      <c r="F125" t="s">
+        <v>33</v>
+      </c>
+      <c r="G125" t="s">
+        <v>34</v>
+      </c>
+      <c r="H125" t="s">
+        <v>35</v>
+      </c>
+      <c r="I125">
+        <v>16</v>
+      </c>
+      <c r="J125" t="s">
+        <v>36</v>
+      </c>
+      <c r="K125">
+        <v>711</v>
+      </c>
+      <c r="L125">
+        <v>1.2503519999999999</v>
+      </c>
+      <c r="M125">
+        <v>63.375</v>
+      </c>
+      <c r="N125" t="s">
+        <v>53</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>1014</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>65</v>
+      </c>
+      <c r="R125">
+        <v>889</v>
+      </c>
+      <c r="S125">
+        <v>1140.607424</v>
+      </c>
+      <c r="T125">
+        <v>16</v>
+      </c>
+      <c r="V125">
+        <v>63.375</v>
+      </c>
+      <c r="W125">
+        <v>1.7997749999999999</v>
+      </c>
+      <c r="X125">
+        <v>22</v>
+      </c>
+      <c r="Y125">
+        <v>2.474691</v>
+      </c>
+      <c r="Z125">
+        <v>46.090909000000003</v>
+      </c>
+      <c r="AA125">
+        <v>3</v>
+      </c>
+      <c r="AB125">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="126" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>28</v>
+      </c>
+      <c r="B126" t="s">
+        <v>29</v>
+      </c>
+      <c r="C126" t="s">
+        <v>66</v>
+      </c>
+      <c r="D126" t="s">
+        <v>31</v>
+      </c>
+      <c r="E126" t="s">
+        <v>32</v>
+      </c>
+      <c r="F126" t="s">
+        <v>56</v>
+      </c>
+      <c r="G126" t="s">
+        <v>34</v>
+      </c>
+      <c r="H126" t="s">
+        <v>35</v>
+      </c>
+      <c r="K126">
+        <v>2</v>
+      </c>
+      <c r="L126">
+        <v>1</v>
+      </c>
+      <c r="N126" t="s">
+        <v>53</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>2</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>65</v>
+      </c>
+      <c r="R126">
+        <v>2</v>
+      </c>
+      <c r="S126">
+        <v>1000</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
+        <v>29</v>
+      </c>
+      <c r="C127" t="s">
+        <v>66</v>
+      </c>
+      <c r="D127" t="s">
+        <v>31</v>
+      </c>
+      <c r="E127" t="s">
+        <v>39</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127" t="s">
+        <v>34</v>
+      </c>
+      <c r="H127" t="s">
+        <v>35</v>
+      </c>
+      <c r="K127">
+        <v>7</v>
+      </c>
+      <c r="L127">
+        <v>1.428571</v>
+      </c>
+      <c r="N127" t="s">
+        <v>53</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>5</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>65</v>
+      </c>
+      <c r="R127">
+        <v>10</v>
+      </c>
+      <c r="S127">
+        <v>500</v>
+      </c>
+      <c r="X127">
+        <v>0</v>
+      </c>
+      <c r="Y127">
+        <v>0</v>
+      </c>
+      <c r="Z127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
+        <v>29</v>
+      </c>
+      <c r="C128" t="s">
+        <v>66</v>
+      </c>
+      <c r="D128" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" t="s">
+        <v>33</v>
+      </c>
+      <c r="G128" t="s">
+        <v>34</v>
+      </c>
+      <c r="H128" t="s">
+        <v>35</v>
+      </c>
+      <c r="I128">
+        <v>16</v>
+      </c>
+      <c r="J128" t="s">
+        <v>36</v>
+      </c>
+      <c r="K128">
+        <v>568</v>
+      </c>
+      <c r="L128">
+        <v>1.3345070000000001</v>
+      </c>
+      <c r="M128">
+        <v>57.4375</v>
+      </c>
+      <c r="N128" t="s">
+        <v>53</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>919</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>65</v>
+      </c>
+      <c r="R128">
+        <v>758</v>
+      </c>
+      <c r="S128">
+        <v>1212.401055</v>
+      </c>
+      <c r="T128">
+        <v>16</v>
+      </c>
+      <c r="V128">
+        <v>57.4375</v>
+      </c>
+      <c r="W128">
+        <v>2.1108180000000001</v>
+      </c>
+      <c r="X128">
+        <v>20</v>
+      </c>
+      <c r="Y128">
+        <v>2.638522</v>
+      </c>
+      <c r="Z128">
+        <v>45.95</v>
+      </c>
+    </row>
+    <row r="129" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
+        <v>29</v>
+      </c>
+      <c r="C129" t="s">
+        <v>66</v>
+      </c>
+      <c r="D129" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" t="s">
+        <v>33</v>
+      </c>
+      <c r="G129" t="s">
+        <v>34</v>
+      </c>
+      <c r="H129" t="s">
+        <v>35</v>
+      </c>
+      <c r="I129">
+        <v>101</v>
+      </c>
+      <c r="J129" t="s">
+        <v>36</v>
+      </c>
+      <c r="K129">
+        <v>1569</v>
+      </c>
+      <c r="L129">
+        <v>1.277247</v>
+      </c>
+      <c r="M129">
+        <v>47.613861389999997</v>
+      </c>
+      <c r="N129" t="s">
+        <v>53</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>4809</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>65</v>
+      </c>
+      <c r="R129">
+        <v>2004</v>
+      </c>
+      <c r="S129">
+        <v>2399.7005989999998</v>
+      </c>
+      <c r="T129">
+        <v>101</v>
+      </c>
+      <c r="V129">
+        <v>47.613861</v>
+      </c>
+      <c r="W129">
+        <v>5.0399200000000004</v>
+      </c>
+      <c r="X129">
+        <v>111</v>
+      </c>
+      <c r="Y129">
+        <v>5.5389220000000003</v>
+      </c>
+      <c r="Z129">
+        <v>43.324323999999997</v>
+      </c>
+      <c r="AA129">
+        <v>2</v>
+      </c>
+      <c r="AB129">
+        <v>2404.5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" t="s">
+        <v>29</v>
+      </c>
+      <c r="C130" t="s">
+        <v>66</v>
+      </c>
+      <c r="D130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E130" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" t="s">
+        <v>56</v>
+      </c>
+      <c r="G130" t="s">
+        <v>34</v>
+      </c>
+      <c r="H130" t="s">
+        <v>35</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+      <c r="L130">
+        <v>1</v>
+      </c>
+      <c r="N130" t="s">
+        <v>53</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>65</v>
+      </c>
+      <c r="R130">
+        <v>1</v>
+      </c>
+      <c r="S130">
+        <v>1000</v>
+      </c>
+      <c r="X130">
+        <v>0</v>
+      </c>
+      <c r="Y130">
+        <v>0</v>
+      </c>
+      <c r="Z130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>28</v>
+      </c>
+      <c r="B131" t="s">
+        <v>29</v>
+      </c>
+      <c r="C131" t="s">
+        <v>64</v>
+      </c>
+      <c r="D131" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" t="s">
+        <v>32</v>
+      </c>
+      <c r="F131" t="s">
+        <v>33</v>
+      </c>
+      <c r="G131" t="s">
+        <v>63</v>
+      </c>
+      <c r="H131" t="s">
+        <v>35</v>
+      </c>
+      <c r="I131">
+        <v>157</v>
+      </c>
+      <c r="J131" t="s">
+        <v>36</v>
+      </c>
+      <c r="K131">
+        <v>2187</v>
+      </c>
+      <c r="L131">
+        <v>1.389575</v>
+      </c>
+      <c r="M131">
+        <v>14.77707006</v>
+      </c>
+      <c r="N131" t="s">
+        <v>53</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>2320</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>62</v>
+      </c>
+      <c r="R131">
+        <v>3039</v>
+      </c>
+      <c r="S131">
+        <v>763.40901599999995</v>
+      </c>
+      <c r="T131">
+        <v>157</v>
+      </c>
+      <c r="V131">
+        <v>14.77707</v>
+      </c>
+      <c r="W131">
+        <v>5.1661729999999997</v>
+      </c>
+      <c r="X131">
+        <v>193</v>
+      </c>
+      <c r="Y131">
+        <v>6.3507730000000002</v>
+      </c>
+      <c r="Z131">
+        <v>12.020725000000001</v>
+      </c>
+      <c r="AA131">
+        <v>127</v>
+      </c>
+      <c r="AB131">
+        <v>18.267717000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132" t="s">
+        <v>29</v>
+      </c>
+      <c r="C132" t="s">
+        <v>64</v>
+      </c>
+      <c r="D132" t="s">
+        <v>31</v>
+      </c>
+      <c r="E132" t="s">
+        <v>32</v>
+      </c>
+      <c r="F132" t="s">
+        <v>56</v>
+      </c>
+      <c r="G132" t="s">
+        <v>63</v>
+      </c>
+      <c r="H132" t="s">
+        <v>35</v>
+      </c>
+      <c r="K132">
+        <v>3</v>
+      </c>
+      <c r="L132">
+        <v>1</v>
+      </c>
+      <c r="N132" t="s">
+        <v>53</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>62</v>
+      </c>
+      <c r="R132">
+        <v>3</v>
+      </c>
+      <c r="S132">
+        <v>333.33333299999998</v>
+      </c>
+      <c r="X132">
+        <v>0</v>
+      </c>
+      <c r="Y132">
+        <v>0</v>
+      </c>
+      <c r="Z132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>28</v>
+      </c>
+      <c r="B133" t="s">
+        <v>29</v>
+      </c>
+      <c r="C133" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" t="s">
+        <v>31</v>
+      </c>
+      <c r="E133" t="s">
+        <v>39</v>
+      </c>
+      <c r="F133" t="s">
+        <v>33</v>
+      </c>
+      <c r="G133" t="s">
+        <v>63</v>
+      </c>
+      <c r="H133" t="s">
+        <v>35</v>
+      </c>
+      <c r="I133">
+        <v>4</v>
+      </c>
+      <c r="J133" t="s">
+        <v>36</v>
+      </c>
+      <c r="K133">
+        <v>66</v>
+      </c>
+      <c r="L133">
+        <v>1.287879</v>
+      </c>
+      <c r="M133">
+        <v>11.75</v>
+      </c>
+      <c r="N133" t="s">
+        <v>53</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>47</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>62</v>
+      </c>
+      <c r="R133">
+        <v>85</v>
+      </c>
+      <c r="S133">
+        <v>552.94117600000004</v>
+      </c>
+      <c r="T133">
+        <v>4</v>
+      </c>
+      <c r="V133">
+        <v>11.75</v>
+      </c>
+      <c r="W133">
+        <v>4.7058819999999999</v>
+      </c>
+      <c r="X133">
+        <v>4</v>
+      </c>
+      <c r="Y133">
+        <v>4.7058819999999999</v>
+      </c>
+      <c r="Z133">
+        <v>11.75</v>
+      </c>
+      <c r="AA133">
+        <v>3</v>
+      </c>
+      <c r="AB133">
+        <v>15.666667</v>
+      </c>
+    </row>
+    <row r="134" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>28</v>
+      </c>
+      <c r="B134" t="s">
+        <v>29</v>
+      </c>
+      <c r="C134" t="s">
+        <v>64</v>
+      </c>
+      <c r="D134" t="s">
+        <v>31</v>
+      </c>
+      <c r="E134" t="s">
+        <v>40</v>
+      </c>
+      <c r="F134" t="s">
+        <v>33</v>
+      </c>
+      <c r="G134" t="s">
+        <v>63</v>
+      </c>
+      <c r="H134" t="s">
+        <v>35</v>
+      </c>
+      <c r="I134">
+        <v>13</v>
+      </c>
+      <c r="J134" t="s">
+        <v>36</v>
+      </c>
+      <c r="K134">
+        <v>275</v>
+      </c>
+      <c r="L134">
+        <v>1.3709089999999999</v>
+      </c>
+      <c r="M134">
+        <v>5.6153846200000004</v>
+      </c>
+      <c r="N134" t="s">
+        <v>53</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>73</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>62</v>
+      </c>
+      <c r="R134">
+        <v>377</v>
+      </c>
+      <c r="S134">
+        <v>193.63395199999999</v>
+      </c>
+      <c r="T134">
+        <v>13</v>
+      </c>
+      <c r="V134">
+        <v>5.6153849999999998</v>
+      </c>
+      <c r="W134">
+        <v>3.4482759999999999</v>
+      </c>
+      <c r="X134">
+        <v>16</v>
+      </c>
+      <c r="Y134">
+        <v>4.2440319999999998</v>
+      </c>
+      <c r="Z134">
+        <v>4.5625</v>
+      </c>
+      <c r="AA134">
+        <v>11</v>
+      </c>
+      <c r="AB134">
+        <v>6.6363640000000004</v>
+      </c>
+    </row>
+    <row r="135" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>28</v>
+      </c>
+      <c r="B135" t="s">
+        <v>29</v>
+      </c>
+      <c r="C135" t="s">
+        <v>64</v>
+      </c>
+      <c r="D135" t="s">
+        <v>31</v>
+      </c>
+      <c r="E135" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" t="s">
+        <v>33</v>
+      </c>
+      <c r="G135" t="s">
+        <v>63</v>
+      </c>
+      <c r="H135" t="s">
+        <v>35</v>
+      </c>
+      <c r="I135">
+        <v>62</v>
+      </c>
+      <c r="J135" t="s">
+        <v>36</v>
+      </c>
+      <c r="K135">
+        <v>1138</v>
+      </c>
+      <c r="L135">
+        <v>1.326889</v>
+      </c>
+      <c r="M135">
+        <v>16.096774190000001</v>
+      </c>
+      <c r="N135" t="s">
+        <v>53</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>998</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>62</v>
+      </c>
+      <c r="R135">
+        <v>1510</v>
+      </c>
+      <c r="S135">
+        <v>660.92715199999998</v>
+      </c>
+      <c r="T135">
+        <v>62</v>
+      </c>
+      <c r="V135">
+        <v>16.096774</v>
+      </c>
+      <c r="W135">
+        <v>4.1059599999999996</v>
+      </c>
+      <c r="X135">
+        <v>75</v>
+      </c>
+      <c r="Y135">
+        <v>4.9668869999999998</v>
+      </c>
+      <c r="Z135">
+        <v>13.306666999999999</v>
+      </c>
+      <c r="AA135">
+        <v>49</v>
+      </c>
+      <c r="AB135">
+        <v>20.367346999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>28</v>
+      </c>
+      <c r="B136" t="s">
+        <v>29</v>
+      </c>
+      <c r="C136" t="s">
+        <v>64</v>
+      </c>
+      <c r="D136" t="s">
+        <v>31</v>
+      </c>
+      <c r="E136" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" t="s">
+        <v>33</v>
+      </c>
+      <c r="G136" t="s">
+        <v>63</v>
+      </c>
+      <c r="H136" t="s">
+        <v>35</v>
+      </c>
+      <c r="I136">
+        <v>157</v>
+      </c>
+      <c r="J136" t="s">
+        <v>36</v>
+      </c>
+      <c r="K136">
+        <v>1784</v>
+      </c>
+      <c r="L136">
+        <v>1.45852</v>
+      </c>
+      <c r="M136">
+        <v>14.89171975</v>
+      </c>
+      <c r="N136" t="s">
+        <v>53</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>2338</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>62</v>
+      </c>
+      <c r="R136">
+        <v>2602</v>
+      </c>
+      <c r="S136">
+        <v>898.53958499999999</v>
+      </c>
+      <c r="T136">
+        <v>157</v>
+      </c>
+      <c r="V136">
+        <v>14.891719999999999</v>
+      </c>
+      <c r="W136">
+        <v>6.0338200000000004</v>
+      </c>
+      <c r="X136">
+        <v>185</v>
+      </c>
+      <c r="Y136">
+        <v>7.109915</v>
+      </c>
+      <c r="Z136">
+        <v>12.637838</v>
+      </c>
+      <c r="AA136">
+        <v>138</v>
+      </c>
+      <c r="AB136">
+        <v>16.942029000000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" t="s">
+        <v>29</v>
+      </c>
+      <c r="C137" t="s">
+        <v>64</v>
+      </c>
+      <c r="D137" t="s">
+        <v>31</v>
+      </c>
+      <c r="E137" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" t="s">
+        <v>56</v>
+      </c>
+      <c r="G137" t="s">
+        <v>63</v>
+      </c>
+      <c r="H137" t="s">
+        <v>35</v>
+      </c>
+      <c r="K137">
+        <v>2</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="N137" t="s">
+        <v>53</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>2</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>62</v>
+      </c>
+      <c r="R137">
+        <v>2</v>
+      </c>
+      <c r="S137">
+        <v>1000</v>
+      </c>
+      <c r="X137">
+        <v>0</v>
+      </c>
+      <c r="Y137">
+        <v>0</v>
+      </c>
+      <c r="Z137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" t="s">
+        <v>29</v>
+      </c>
+      <c r="C138" t="s">
+        <v>61</v>
+      </c>
+      <c r="D138" t="s">
+        <v>31</v>
+      </c>
+      <c r="E138" t="s">
+        <v>32</v>
+      </c>
+      <c r="F138" t="s">
+        <v>33</v>
+      </c>
+      <c r="G138" t="s">
+        <v>34</v>
+      </c>
+      <c r="H138" t="s">
+        <v>35</v>
+      </c>
+      <c r="I138">
+        <v>11</v>
+      </c>
+      <c r="J138" t="s">
+        <v>36</v>
+      </c>
+      <c r="K138">
+        <v>365</v>
+      </c>
+      <c r="L138">
+        <v>1.4657530000000001</v>
+      </c>
+      <c r="M138">
+        <v>59.81818182</v>
+      </c>
+      <c r="N138" t="s">
+        <v>53</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>658</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>60</v>
+      </c>
+      <c r="R138">
+        <v>535</v>
+      </c>
+      <c r="S138">
+        <v>1229.9065419999999</v>
+      </c>
+      <c r="T138">
+        <v>11</v>
+      </c>
+      <c r="V138">
+        <v>59.818182</v>
+      </c>
+      <c r="W138">
+        <v>2.0560749999999999</v>
+      </c>
+      <c r="X138">
+        <v>10</v>
+      </c>
+      <c r="Y138">
+        <v>1.869159</v>
+      </c>
+      <c r="Z138">
+        <v>65.8</v>
+      </c>
+      <c r="AA138">
+        <v>7</v>
+      </c>
+      <c r="AB138">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="139" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>28</v>
+      </c>
+      <c r="B139" t="s">
+        <v>29</v>
+      </c>
+      <c r="C139" t="s">
+        <v>61</v>
+      </c>
+      <c r="D139" t="s">
+        <v>31</v>
+      </c>
+      <c r="E139" t="s">
+        <v>39</v>
+      </c>
+      <c r="F139" t="s">
+        <v>33</v>
+      </c>
+      <c r="G139" t="s">
+        <v>34</v>
+      </c>
+      <c r="H139" t="s">
+        <v>35</v>
+      </c>
+      <c r="K139">
+        <v>48</v>
+      </c>
+      <c r="L139">
+        <v>1.2916669999999999</v>
+      </c>
+      <c r="N139" t="s">
+        <v>53</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>35</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>60</v>
+      </c>
+      <c r="R139">
+        <v>62</v>
+      </c>
+      <c r="S139">
+        <v>564.51612899999998</v>
+      </c>
+      <c r="X139">
+        <v>0</v>
+      </c>
+      <c r="Y139">
+        <v>0</v>
+      </c>
+      <c r="Z139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
+        <v>29</v>
+      </c>
+      <c r="C140" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
+        <v>31</v>
+      </c>
+      <c r="E140" t="s">
+        <v>40</v>
+      </c>
+      <c r="F140" t="s">
+        <v>33</v>
+      </c>
+      <c r="G140" t="s">
+        <v>34</v>
+      </c>
+      <c r="H140" t="s">
+        <v>35</v>
+      </c>
+      <c r="K140">
+        <v>18</v>
+      </c>
+      <c r="L140">
+        <v>1.1666669999999999</v>
+      </c>
+      <c r="N140" t="s">
+        <v>53</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>8</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>60</v>
+      </c>
+      <c r="R140">
+        <v>21</v>
+      </c>
+      <c r="S140">
+        <v>380.952381</v>
+      </c>
+      <c r="X140">
+        <v>0</v>
+      </c>
+      <c r="Y140">
+        <v>0</v>
+      </c>
+      <c r="Z140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>28</v>
+      </c>
+      <c r="B141" t="s">
+        <v>29</v>
+      </c>
+      <c r="C141" t="s">
+        <v>61</v>
+      </c>
+      <c r="D141" t="s">
+        <v>31</v>
+      </c>
+      <c r="E141" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" t="s">
+        <v>33</v>
+      </c>
+      <c r="G141" t="s">
+        <v>34</v>
+      </c>
+      <c r="H141" t="s">
+        <v>35</v>
+      </c>
+      <c r="I141">
+        <v>3</v>
+      </c>
+      <c r="J141" t="s">
+        <v>36</v>
+      </c>
+      <c r="K141">
+        <v>324</v>
+      </c>
+      <c r="L141">
+        <v>1.358025</v>
+      </c>
+      <c r="M141">
+        <v>103</v>
+      </c>
+      <c r="N141" t="s">
+        <v>53</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>309</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>60</v>
+      </c>
+      <c r="R141">
+        <v>440</v>
+      </c>
+      <c r="S141">
+        <v>702.27272700000003</v>
+      </c>
+      <c r="T141">
+        <v>3</v>
+      </c>
+      <c r="V141">
+        <v>103</v>
+      </c>
+      <c r="W141">
+        <v>0.68181800000000004</v>
+      </c>
+      <c r="X141">
+        <v>4</v>
+      </c>
+      <c r="Y141">
+        <v>0.90909099999999998</v>
+      </c>
+      <c r="Z141">
+        <v>77.25</v>
+      </c>
+      <c r="AA141">
+        <v>2</v>
+      </c>
+      <c r="AB141">
+        <v>154.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>28</v>
+      </c>
+      <c r="B142" t="s">
+        <v>29</v>
+      </c>
+      <c r="C142" t="s">
+        <v>61</v>
+      </c>
+      <c r="D142" t="s">
+        <v>31</v>
+      </c>
+      <c r="E142" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142" t="s">
+        <v>33</v>
+      </c>
+      <c r="G142" t="s">
+        <v>34</v>
+      </c>
+      <c r="H142" t="s">
+        <v>35</v>
+      </c>
+      <c r="I142">
+        <v>98</v>
+      </c>
+      <c r="J142" t="s">
+        <v>36</v>
+      </c>
+      <c r="K142">
+        <v>4626</v>
+      </c>
+      <c r="L142">
+        <v>1.579334</v>
+      </c>
+      <c r="M142">
+        <v>55.959183670000002</v>
+      </c>
+      <c r="N142" t="s">
+        <v>53</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>5484</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>60</v>
+      </c>
+      <c r="R142">
+        <v>7306</v>
+      </c>
+      <c r="S142">
+        <v>750.61593200000004</v>
+      </c>
+      <c r="T142">
+        <v>98</v>
+      </c>
+      <c r="V142">
+        <v>55.959184</v>
+      </c>
+      <c r="W142">
+        <v>1.3413630000000001</v>
+      </c>
+      <c r="X142">
+        <v>101</v>
+      </c>
+      <c r="Y142">
+        <v>1.382425</v>
+      </c>
+      <c r="Z142">
+        <v>54.297029999999999</v>
+      </c>
+      <c r="AA142">
+        <v>53</v>
+      </c>
+      <c r="AB142">
+        <v>103.471698</v>
+      </c>
+    </row>
+    <row r="143" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" t="s">
+        <v>29</v>
+      </c>
+      <c r="C143" t="s">
+        <v>59</v>
+      </c>
+      <c r="D143" t="s">
+        <v>31</v>
+      </c>
+      <c r="E143" t="s">
+        <v>32</v>
+      </c>
+      <c r="F143" t="s">
+        <v>33</v>
+      </c>
+      <c r="G143" t="s">
+        <v>34</v>
+      </c>
+      <c r="H143" t="s">
+        <v>35</v>
+      </c>
+      <c r="I143">
+        <v>86</v>
+      </c>
+      <c r="J143" t="s">
+        <v>36</v>
+      </c>
+      <c r="K143">
+        <v>1845</v>
+      </c>
+      <c r="L143">
+        <v>1.570732</v>
+      </c>
+      <c r="M143">
+        <v>29.872093020000001</v>
+      </c>
+      <c r="N143" t="s">
+        <v>53</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>2569</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>58</v>
+      </c>
+      <c r="R143">
+        <v>2898</v>
+      </c>
+      <c r="S143">
+        <v>886.47343000000001</v>
+      </c>
+      <c r="T143">
+        <v>86</v>
+      </c>
+      <c r="V143">
+        <v>29.872093</v>
+      </c>
+      <c r="W143">
+        <v>2.9675639999999999</v>
+      </c>
+      <c r="X143">
+        <v>95</v>
+      </c>
+      <c r="Y143">
+        <v>3.2781229999999999</v>
+      </c>
+      <c r="Z143">
+        <v>27.042104999999999</v>
+      </c>
+      <c r="AA143">
+        <v>76</v>
+      </c>
+      <c r="AB143">
+        <v>33.802632000000003</v>
+      </c>
+    </row>
+    <row r="144" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144" t="s">
+        <v>59</v>
+      </c>
+      <c r="D144" t="s">
+        <v>31</v>
+      </c>
+      <c r="E144" t="s">
+        <v>39</v>
+      </c>
+      <c r="F144" t="s">
+        <v>33</v>
+      </c>
+      <c r="G144" t="s">
+        <v>34</v>
+      </c>
+      <c r="H144" t="s">
+        <v>35</v>
+      </c>
+      <c r="K144">
+        <v>41</v>
+      </c>
+      <c r="L144">
+        <v>1.292683</v>
+      </c>
+      <c r="N144" t="s">
+        <v>53</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>34</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>58</v>
+      </c>
+      <c r="R144">
+        <v>53</v>
+      </c>
+      <c r="S144">
+        <v>641.50943400000006</v>
+      </c>
+      <c r="X144">
+        <v>0</v>
+      </c>
+      <c r="Y144">
+        <v>0</v>
+      </c>
+      <c r="Z144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>28</v>
+      </c>
+      <c r="B145" t="s">
+        <v>29</v>
+      </c>
+      <c r="C145" t="s">
+        <v>59</v>
+      </c>
+      <c r="D145" t="s">
+        <v>31</v>
+      </c>
+      <c r="E145" t="s">
+        <v>40</v>
+      </c>
+      <c r="F145" t="s">
+        <v>33</v>
+      </c>
+      <c r="G145" t="s">
+        <v>34</v>
+      </c>
+      <c r="H145" t="s">
+        <v>35</v>
+      </c>
+      <c r="K145">
+        <v>52</v>
+      </c>
+      <c r="L145">
+        <v>1.3076920000000001</v>
+      </c>
+      <c r="N145" t="s">
+        <v>53</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>13</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>58</v>
+      </c>
+      <c r="R145">
+        <v>68</v>
+      </c>
+      <c r="S145">
+        <v>191.17647099999999</v>
+      </c>
+      <c r="X145">
+        <v>0</v>
+      </c>
+      <c r="Y145">
+        <v>0</v>
+      </c>
+      <c r="Z145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>28</v>
+      </c>
+      <c r="B146" t="s">
+        <v>29</v>
+      </c>
+      <c r="C146" t="s">
+        <v>59</v>
+      </c>
+      <c r="D146" t="s">
+        <v>31</v>
+      </c>
+      <c r="E146" t="s">
+        <v>41</v>
+      </c>
+      <c r="F146" t="s">
+        <v>33</v>
+      </c>
+      <c r="G146" t="s">
+        <v>34</v>
+      </c>
+      <c r="H146" t="s">
+        <v>35</v>
+      </c>
+      <c r="I146">
+        <v>71</v>
+      </c>
+      <c r="J146" t="s">
+        <v>36</v>
+      </c>
+      <c r="K146">
+        <v>1368</v>
+      </c>
+      <c r="L146">
+        <v>1.4546779999999999</v>
+      </c>
+      <c r="M146">
+        <v>28.422535209999999</v>
+      </c>
+      <c r="N146" t="s">
+        <v>53</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>2018</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>58</v>
+      </c>
+      <c r="R146">
+        <v>1990</v>
+      </c>
+      <c r="S146">
+        <v>1014.070352</v>
+      </c>
+      <c r="T146">
+        <v>71</v>
+      </c>
+      <c r="V146">
+        <v>28.422535</v>
+      </c>
+      <c r="W146">
+        <v>3.5678390000000002</v>
+      </c>
+      <c r="X146">
+        <v>78</v>
+      </c>
+      <c r="Y146">
+        <v>3.9195980000000001</v>
+      </c>
+      <c r="Z146">
+        <v>25.871794999999999</v>
+      </c>
+      <c r="AA146">
+        <v>65</v>
+      </c>
+      <c r="AB146">
+        <v>31.046154000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" t="s">
+        <v>29</v>
+      </c>
+      <c r="C147" t="s">
+        <v>59</v>
+      </c>
+      <c r="D147" t="s">
+        <v>31</v>
+      </c>
+      <c r="E147" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147" t="s">
+        <v>33</v>
+      </c>
+      <c r="G147" t="s">
+        <v>34</v>
+      </c>
+      <c r="H147" t="s">
+        <v>35</v>
+      </c>
+      <c r="I147">
+        <v>44</v>
+      </c>
+      <c r="J147" t="s">
+        <v>36</v>
+      </c>
+      <c r="K147">
+        <v>831</v>
+      </c>
+      <c r="L147">
+        <v>1.392298</v>
+      </c>
+      <c r="M147">
+        <v>34.409090910000003</v>
+      </c>
+      <c r="N147" t="s">
+        <v>53</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>1514</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>58</v>
+      </c>
+      <c r="R147">
+        <v>1157</v>
+      </c>
+      <c r="S147">
+        <v>1308.5566120000001</v>
+      </c>
+      <c r="T147">
+        <v>44</v>
+      </c>
+      <c r="V147">
+        <v>34.409090999999997</v>
+      </c>
+      <c r="W147">
+        <v>3.8029389999999998</v>
+      </c>
+      <c r="X147">
+        <v>48</v>
+      </c>
+      <c r="Y147">
+        <v>4.1486599999999996</v>
+      </c>
+      <c r="Z147">
+        <v>31.541667</v>
+      </c>
+      <c r="AA147">
+        <v>38</v>
+      </c>
+      <c r="AB147">
+        <v>39.842104999999997</v>
+      </c>
+    </row>
+    <row r="148" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>28</v>
+      </c>
+      <c r="B148" t="s">
+        <v>29</v>
+      </c>
+      <c r="C148" t="s">
+        <v>59</v>
+      </c>
+      <c r="D148" t="s">
+        <v>31</v>
+      </c>
+      <c r="E148" t="s">
+        <v>42</v>
+      </c>
+      <c r="F148" t="s">
+        <v>56</v>
+      </c>
+      <c r="G148" t="s">
+        <v>34</v>
+      </c>
+      <c r="H148" t="s">
+        <v>35</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>1</v>
+      </c>
+      <c r="N148" t="s">
+        <v>53</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>58</v>
+      </c>
+      <c r="R148">
+        <v>1</v>
+      </c>
+      <c r="S148">
+        <v>1000</v>
+      </c>
+      <c r="X148">
+        <v>0</v>
+      </c>
+      <c r="Y148">
+        <v>0</v>
+      </c>
+      <c r="Z148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>28</v>
+      </c>
+      <c r="B149" t="s">
+        <v>29</v>
+      </c>
+      <c r="C149" t="s">
+        <v>57</v>
+      </c>
+      <c r="D149" t="s">
+        <v>31</v>
+      </c>
+      <c r="E149" t="s">
+        <v>32</v>
+      </c>
+      <c r="F149" t="s">
+        <v>33</v>
+      </c>
+      <c r="G149" t="s">
+        <v>34</v>
+      </c>
+      <c r="H149" t="s">
+        <v>35</v>
+      </c>
+      <c r="I149">
+        <v>18</v>
+      </c>
+      <c r="J149" t="s">
+        <v>36</v>
+      </c>
+      <c r="K149">
+        <v>912</v>
+      </c>
+      <c r="L149">
+        <v>1.4528509999999999</v>
+      </c>
+      <c r="M149">
+        <v>49.388888889999997</v>
+      </c>
+      <c r="N149" t="s">
+        <v>53</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>889</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>55</v>
+      </c>
+      <c r="R149">
+        <v>1325</v>
+      </c>
+      <c r="S149">
+        <v>670.94339600000001</v>
+      </c>
+      <c r="T149">
+        <v>18</v>
+      </c>
+      <c r="V149">
+        <v>49.388888999999999</v>
+      </c>
+      <c r="W149">
+        <v>1.3584909999999999</v>
+      </c>
+      <c r="X149">
+        <v>26</v>
+      </c>
+      <c r="Y149">
+        <v>1.962264</v>
+      </c>
+      <c r="Z149">
+        <v>34.192307999999997</v>
+      </c>
+      <c r="AA149">
+        <v>17</v>
+      </c>
+      <c r="AB149">
+        <v>52.294117999999997</v>
+      </c>
+    </row>
+    <row r="150" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>28</v>
+      </c>
+      <c r="B150" t="s">
+        <v>29</v>
+      </c>
+      <c r="C150" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150" t="s">
+        <v>31</v>
+      </c>
+      <c r="E150" t="s">
+        <v>32</v>
+      </c>
+      <c r="F150" t="s">
+        <v>56</v>
+      </c>
+      <c r="G150" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" t="s">
+        <v>35</v>
+      </c>
+      <c r="K150">
+        <v>2</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="N150" t="s">
+        <v>53</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>2</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>55</v>
+      </c>
+      <c r="R150">
+        <v>2</v>
+      </c>
+      <c r="S150">
+        <v>1000</v>
+      </c>
+      <c r="X150">
+        <v>0</v>
+      </c>
+      <c r="Y150">
+        <v>0</v>
+      </c>
+      <c r="Z150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>28</v>
+      </c>
+      <c r="B151" t="s">
+        <v>29</v>
+      </c>
+      <c r="C151" t="s">
+        <v>57</v>
+      </c>
+      <c r="D151" t="s">
+        <v>31</v>
+      </c>
+      <c r="E151" t="s">
+        <v>39</v>
+      </c>
+      <c r="F151" t="s">
+        <v>33</v>
+      </c>
+      <c r="G151" t="s">
+        <v>34</v>
+      </c>
+      <c r="H151" t="s">
+        <v>35</v>
+      </c>
+      <c r="I151">
+        <v>2</v>
+      </c>
+      <c r="J151" t="s">
+        <v>36</v>
+      </c>
+      <c r="K151">
+        <v>52</v>
+      </c>
+      <c r="L151">
+        <v>1.1538459999999999</v>
+      </c>
+      <c r="M151">
+        <v>16</v>
+      </c>
+      <c r="N151" t="s">
+        <v>53</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>32</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>55</v>
+      </c>
+      <c r="R151">
+        <v>60</v>
+      </c>
+      <c r="S151">
+        <v>533.33333300000004</v>
+      </c>
+      <c r="T151">
+        <v>2</v>
+      </c>
+      <c r="V151">
+        <v>16</v>
+      </c>
+      <c r="W151">
+        <v>3.3333330000000001</v>
+      </c>
+      <c r="X151">
+        <v>2</v>
+      </c>
+      <c r="Y151">
+        <v>3.3333330000000001</v>
+      </c>
+      <c r="Z151">
+        <v>16</v>
+      </c>
+      <c r="AA151">
+        <v>2</v>
+      </c>
+      <c r="AB151">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>28</v>
+      </c>
+      <c r="B152" t="s">
+        <v>29</v>
+      </c>
+      <c r="C152" t="s">
+        <v>57</v>
+      </c>
+      <c r="D152" t="s">
+        <v>31</v>
+      </c>
+      <c r="E152" t="s">
+        <v>40</v>
+      </c>
+      <c r="F152" t="s">
+        <v>33</v>
+      </c>
+      <c r="G152" t="s">
+        <v>34</v>
+      </c>
+      <c r="H152" t="s">
+        <v>35</v>
+      </c>
+      <c r="K152">
+        <v>47</v>
+      </c>
+      <c r="L152">
+        <v>1.2553190000000001</v>
+      </c>
+      <c r="N152" t="s">
+        <v>53</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>10</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>55</v>
+      </c>
+      <c r="R152">
+        <v>59</v>
+      </c>
+      <c r="S152">
+        <v>169.491525</v>
+      </c>
+      <c r="X152">
+        <v>0</v>
+      </c>
+      <c r="Y152">
+        <v>0</v>
+      </c>
+      <c r="Z152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" t="s">
+        <v>29</v>
+      </c>
+      <c r="C153" t="s">
+        <v>57</v>
+      </c>
+      <c r="D153" t="s">
+        <v>31</v>
+      </c>
+      <c r="E153" t="s">
+        <v>41</v>
+      </c>
+      <c r="F153" t="s">
+        <v>33</v>
+      </c>
+      <c r="G153" t="s">
+        <v>34</v>
+      </c>
+      <c r="H153" t="s">
+        <v>35</v>
+      </c>
+      <c r="I153">
+        <v>19</v>
+      </c>
+      <c r="J153" t="s">
+        <v>36</v>
+      </c>
+      <c r="K153">
+        <v>587</v>
+      </c>
+      <c r="L153">
+        <v>1.354344</v>
+      </c>
+      <c r="M153">
+        <v>26.05263158</v>
+      </c>
+      <c r="N153" t="s">
+        <v>53</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>495</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>55</v>
+      </c>
+      <c r="R153">
+        <v>795</v>
+      </c>
+      <c r="S153">
+        <v>622.64150900000004</v>
+      </c>
+      <c r="T153">
+        <v>19</v>
+      </c>
+      <c r="V153">
+        <v>26.052631999999999</v>
+      </c>
+      <c r="W153">
+        <v>2.3899370000000002</v>
+      </c>
+      <c r="X153">
+        <v>25</v>
+      </c>
+      <c r="Y153">
+        <v>3.1446540000000001</v>
+      </c>
+      <c r="Z153">
+        <v>19.8</v>
+      </c>
+      <c r="AA153">
+        <v>13</v>
+      </c>
+      <c r="AB153">
+        <v>38.076923000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" t="s">
+        <v>29</v>
+      </c>
+      <c r="C154" t="s">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>31</v>
+      </c>
+      <c r="E154" t="s">
+        <v>42</v>
+      </c>
+      <c r="F154" t="s">
+        <v>33</v>
+      </c>
+      <c r="G154" t="s">
+        <v>34</v>
+      </c>
+      <c r="H154" t="s">
+        <v>35</v>
+      </c>
+      <c r="I154">
+        <v>115</v>
+      </c>
+      <c r="J154" t="s">
+        <v>36</v>
+      </c>
+      <c r="K154">
+        <v>3164</v>
+      </c>
+      <c r="L154">
+        <v>1.6513910000000001</v>
+      </c>
+      <c r="M154">
+        <v>35.730434780000003</v>
+      </c>
+      <c r="N154" t="s">
+        <v>53</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>4109</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>55</v>
+      </c>
+      <c r="R154">
+        <v>5225</v>
+      </c>
+      <c r="S154">
+        <v>786.41148299999998</v>
+      </c>
+      <c r="T154">
+        <v>115</v>
+      </c>
+      <c r="V154">
+        <v>35.730435</v>
+      </c>
+      <c r="W154">
+        <v>2.2009569999999998</v>
+      </c>
+      <c r="X154">
+        <v>153</v>
+      </c>
+      <c r="Y154">
+        <v>2.9282300000000001</v>
+      </c>
+      <c r="Z154">
+        <v>26.856209</v>
+      </c>
+      <c r="AA154">
+        <v>99</v>
+      </c>
+      <c r="AB154">
+        <v>41.505051000000002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>28</v>
+      </c>
+      <c r="B155" t="s">
+        <v>29</v>
+      </c>
+      <c r="C155" t="s">
+        <v>57</v>
+      </c>
+      <c r="D155" t="s">
+        <v>31</v>
+      </c>
+      <c r="E155" t="s">
+        <v>42</v>
+      </c>
+      <c r="F155" t="s">
+        <v>56</v>
+      </c>
+      <c r="G155" t="s">
+        <v>34</v>
+      </c>
+      <c r="H155" t="s">
+        <v>35</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+      <c r="L155">
+        <v>1</v>
+      </c>
+      <c r="N155" t="s">
+        <v>53</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>55</v>
+      </c>
+      <c r="R155">
+        <v>1</v>
+      </c>
+      <c r="S155">
+        <v>0</v>
+      </c>
+      <c r="X155">
+        <v>0</v>
+      </c>
+      <c r="Y155">
+        <v>0</v>
+      </c>
+      <c r="Z155">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>